--- a/web/报警规则模板.xlsx
+++ b/web/报警规则模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17325"/>
+    <workbookView windowWidth="18352" windowHeight="7605"/>
   </bookViews>
   <sheets>
     <sheet name="重大危险源报警规则" sheetId="3" r:id="rId1"/>
@@ -168,7 +168,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1392" uniqueCount="573">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1384" uniqueCount="566">
   <si>
     <t>d</t>
   </si>
@@ -367,53 +367,6 @@
     <t>备注说明</t>
   </si>
   <si>
-    <t>330405H06A000301</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">填写说明：
-该规则为重大危险源设备特有，配置后默认设备同一规则下最多产生一条报警记录，可根据规则进行报警升级/降级子报警记录通报，若有正常数据上报则立即自动销警。
-首次报警抑制时间：检测值超过阈值后到首次产生报警记录的时间，0代表立即产生报警记录。
-低低报：检测值＜该值时，将产生低低报；
-低报：若低低报无值，则检测值＜该值，将产生低报；若低低报有值，则在低低报≤检测值＜低报范围内，将产生低报；
-高报：若高高报无值，则检测值＞该值，将产生高报；若高高报有值，则在高报＜检测值≤高高报范围内，将产生高报；
-高高报：检测值＞该值时，将产生高高报。
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>要求：低低报&lt;低报&lt;高报&lt;高高报</t>
-    </r>
-  </si>
-  <si>
     <t>光气及光气化工艺</t>
   </si>
   <si>
@@ -2084,14 +2037,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="31">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2289,22 +2235,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
       <color rgb="FFFF0000"/>
       <name val="仿宋"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="14"/>
       <color rgb="FFFF0000"/>
       <name val="仿宋"/>
       <charset val="134"/>
@@ -2546,13 +2485,13 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -2671,13 +2610,16 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2686,123 +2628,120 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2810,62 +2749,49 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -3429,20 +3355,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="21" customWidth="1"/>
     <col min="4" max="4" width="22" customWidth="1"/>
-    <col min="5" max="5" width="19.3666666666667" customWidth="1"/>
-    <col min="6" max="6" width="18.9083333333333" customWidth="1"/>
-    <col min="7" max="7" width="17.9083333333333" customWidth="1"/>
-    <col min="8" max="9" width="13.3666666666667" customWidth="1"/>
+    <col min="5" max="5" width="19.3628318584071" customWidth="1"/>
+    <col min="6" max="6" width="18.9115044247788" customWidth="1"/>
+    <col min="7" max="7" width="17.9115044247788" customWidth="1"/>
+    <col min="8" max="9" width="13.3628318584071" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="11"/>
@@ -3454,7 +3380,7 @@
       <c r="H1" s="11"/>
       <c r="I1" s="11"/>
     </row>
-    <row r="2" ht="18.75" spans="1:9">
+    <row r="2" ht="17.65" spans="1:9">
       <c r="A2" s="12" t="s">
         <v>1</v>
       </c>
@@ -3483,7 +3409,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" ht="94.5" customHeight="1" spans="1:9">
+    <row r="3" s="9" customFormat="1" ht="94.5" customHeight="1" spans="1:9">
       <c r="A3" s="13" t="s">
         <v>10</v>
       </c>
@@ -3508,197 +3434,79 @@
       <c r="H3" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="18" t="s">
+      <c r="I3" s="17" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="21">
-        <v>1</v>
-      </c>
-      <c r="D4" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="I4" s="20"/>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="20"/>
-      <c r="B5" s="20"/>
-      <c r="C5" s="20"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="20"/>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="20"/>
-      <c r="B6" s="20"/>
-      <c r="C6" s="20"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="20"/>
-      <c r="I6" s="20"/>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="20"/>
-      <c r="B7" s="20"/>
-      <c r="C7" s="20"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="20"/>
-      <c r="H7" s="20"/>
-      <c r="I7" s="20"/>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="20"/>
-      <c r="B8" s="20"/>
-      <c r="C8" s="20"/>
-      <c r="D8" s="20"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="20"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="20"/>
-      <c r="I8" s="20"/>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="20"/>
-      <c r="B9" s="20"/>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="20"/>
-      <c r="I9" s="20"/>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="22"/>
-      <c r="B10" s="22"/>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="22"/>
-      <c r="H10" s="22"/>
-      <c r="I10" s="22"/>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="24"/>
-      <c r="C11" s="24"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="24"/>
-      <c r="F11" s="24"/>
-      <c r="G11" s="24"/>
-      <c r="H11" s="24"/>
-      <c r="I11" s="24"/>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12" s="24"/>
-      <c r="B12" s="24"/>
-      <c r="C12" s="24"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="24"/>
-      <c r="F12" s="24"/>
-      <c r="G12" s="24"/>
-      <c r="H12" s="24"/>
-      <c r="I12" s="24"/>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="A13" s="24"/>
-      <c r="B13" s="24"/>
-      <c r="C13" s="24"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="24"/>
-      <c r="G13" s="24"/>
-      <c r="H13" s="24"/>
-      <c r="I13" s="24"/>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" s="24"/>
-      <c r="B14" s="24"/>
-      <c r="C14" s="24"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="24"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="24"/>
-      <c r="I14" s="24"/>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="A15" s="24"/>
-      <c r="B15" s="24"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="24"/>
-      <c r="I15" s="24"/>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="A16" s="24"/>
-      <c r="B16" s="24"/>
-      <c r="C16" s="24"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="24"/>
-      <c r="G16" s="24"/>
-      <c r="H16" s="24"/>
-      <c r="I16" s="24"/>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="A17" s="24"/>
-      <c r="B17" s="24"/>
-      <c r="C17" s="24"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="24"/>
-      <c r="G17" s="24"/>
-      <c r="H17" s="24"/>
-      <c r="I17" s="24"/>
-    </row>
-    <row r="18" spans="1:9">
-      <c r="A18" s="24"/>
-      <c r="B18" s="24"/>
-      <c r="C18" s="24"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="24"/>
-      <c r="H18" s="24"/>
-      <c r="I18" s="24"/>
+    <row r="4" s="10" customFormat="1" spans="1:9">
+      <c r="A4" s="18"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="18"/>
+    </row>
+    <row r="5" s="10" customFormat="1" spans="1:9">
+      <c r="A5" s="18"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="18"/>
+    </row>
+    <row r="6" s="10" customFormat="1" spans="1:9">
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+    </row>
+    <row r="7" s="10" customFormat="1" spans="1:9">
+      <c r="A7" s="18"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="18"/>
+    </row>
+    <row r="8" s="10" customFormat="1" spans="1:9">
+      <c r="A8" s="18"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="18"/>
+    </row>
+    <row r="9" s="10" customFormat="1" spans="1:9">
+      <c r="A9" s="19"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A11:I18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -3711,51 +3519,51 @@
   <dimension ref="A1:Z138"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="46.0916666666667" customWidth="1"/>
-    <col min="2" max="2" width="6.45" customWidth="1"/>
-    <col min="3" max="3" width="97.6333333333333" customWidth="1"/>
-    <col min="4" max="4" width="81.6333333333333" customWidth="1"/>
-    <col min="5" max="5" width="149.091666666667" customWidth="1"/>
-    <col min="6" max="6" width="77.45" customWidth="1"/>
-    <col min="7" max="8" width="67.0916666666667" customWidth="1"/>
-    <col min="9" max="9" width="58.9083333333333" customWidth="1"/>
+    <col min="1" max="1" width="46.0884955752212" customWidth="1"/>
+    <col min="2" max="2" width="6.45132743362832" customWidth="1"/>
+    <col min="3" max="3" width="97.6371681415929" customWidth="1"/>
+    <col min="4" max="4" width="81.6371681415929" customWidth="1"/>
+    <col min="5" max="5" width="149.088495575221" customWidth="1"/>
+    <col min="6" max="6" width="77.4513274336283" customWidth="1"/>
+    <col min="7" max="8" width="67.0884955752212" customWidth="1"/>
+    <col min="9" max="9" width="58.9115044247788" customWidth="1"/>
     <col min="10" max="10" width="38" customWidth="1"/>
-    <col min="11" max="11" width="63.45" customWidth="1"/>
-    <col min="12" max="12" width="53.9083333333333" customWidth="1"/>
-    <col min="13" max="13" width="48.45" customWidth="1"/>
+    <col min="11" max="11" width="63.4513274336283" customWidth="1"/>
+    <col min="12" max="12" width="53.9115044247788" customWidth="1"/>
+    <col min="13" max="13" width="48.4513274336283" customWidth="1"/>
     <col min="14" max="14" width="38" customWidth="1"/>
-    <col min="15" max="15" width="35.9083333333333" customWidth="1"/>
+    <col min="15" max="15" width="35.9115044247788" customWidth="1"/>
     <col min="16" max="16" width="30" customWidth="1"/>
-    <col min="17" max="17" width="40.3666666666667" customWidth="1"/>
-    <col min="18" max="18" width="42.45" customWidth="1"/>
-    <col min="19" max="19" width="52.9083333333333" customWidth="1"/>
-    <col min="20" max="20" width="42.0916666666667" customWidth="1"/>
-    <col min="21" max="21" width="29.6333333333333" customWidth="1"/>
-    <col min="22" max="22" width="33.9083333333333" customWidth="1"/>
-    <col min="23" max="23" width="45.3666666666667" customWidth="1"/>
+    <col min="17" max="17" width="40.3628318584071" customWidth="1"/>
+    <col min="18" max="18" width="42.4513274336283" customWidth="1"/>
+    <col min="19" max="19" width="52.9115044247788" customWidth="1"/>
+    <col min="20" max="20" width="42.0884955752212" customWidth="1"/>
+    <col min="21" max="21" width="29.6371681415929" customWidth="1"/>
+    <col min="22" max="22" width="33.9115044247788" customWidth="1"/>
+    <col min="23" max="23" width="45.3628318584071" customWidth="1"/>
     <col min="24" max="24" width="35" customWidth="1"/>
-    <col min="25" max="25" width="19.0916666666667" customWidth="1"/>
-    <col min="26" max="26" width="31.9083333333333" customWidth="1"/>
+    <col min="25" max="25" width="19.0884955752212" customWidth="1"/>
+    <col min="26" max="26" width="31.9115044247788" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
@@ -3780,16 +3588,16 @@
     </row>
     <row r="2" spans="1:26">
       <c r="A2" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
@@ -3816,19 +3624,19 @@
     </row>
     <row r="3" spans="1:26">
       <c r="A3" s="1" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
@@ -3854,22 +3662,22 @@
     </row>
     <row r="4" spans="1:26">
       <c r="A4" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
@@ -3894,28 +3702,28 @@
     </row>
     <row r="5" spans="1:26">
       <c r="A5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
@@ -3938,31 +3746,31 @@
     </row>
     <row r="6" spans="1:26">
       <c r="A6" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H6" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="I6" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>63</v>
       </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
@@ -3984,28 +3792,28 @@
     </row>
     <row r="7" spans="1:26">
       <c r="A7" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H7" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>71</v>
       </c>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
@@ -4028,37 +3836,37 @@
     </row>
     <row r="8" spans="1:26">
       <c r="A8" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H8" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="I8" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="J8" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="K8" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>82</v>
       </c>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
@@ -4078,25 +3886,25 @@
     </row>
     <row r="9" spans="1:26">
       <c r="A9" s="1" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
@@ -4120,108 +3928,108 @@
     </row>
     <row r="10" spans="1:26">
       <c r="A10" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H10" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="I10" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="J10" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="K10" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="L10" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="M10" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="N10" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="O10" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="P10" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="J10" s="1" t="s">
+      <c r="Q10" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="K10" s="1" t="s">
+      <c r="R10" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="L10" s="1" t="s">
+      <c r="S10" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="M10" s="1" t="s">
+      <c r="T10" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="N10" s="1" t="s">
+      <c r="U10" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="O10" s="1" t="s">
+      <c r="V10" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="P10" s="1" t="s">
+      <c r="W10" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="Q10" s="1" t="s">
+      <c r="X10" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="R10" s="1" t="s">
+      <c r="Y10" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="S10" s="1" t="s">
+      <c r="Z10" s="1" t="s">
         <v>108</v>
-      </c>
-      <c r="T10" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="U10" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="V10" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="W10" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="X10" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="Y10" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="Z10" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:26">
       <c r="A11" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="H11" s="3" t="s">
         <v>116</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>123</v>
       </c>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
@@ -4244,40 +4052,40 @@
     </row>
     <row r="12" spans="1:26">
       <c r="A12" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="H12" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="I12" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="J12" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="K12" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="L12" s="1" t="s">
         <v>128</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="L12" s="1" t="s">
-        <v>135</v>
       </c>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
@@ -4296,40 +4104,40 @@
     </row>
     <row r="13" spans="1:26">
       <c r="A13" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="H13" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="I13" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="J13" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="K13" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="L13" s="1" t="s">
         <v>140</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>147</v>
       </c>
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
@@ -4348,22 +4156,22 @@
     </row>
     <row r="14" spans="1:26">
       <c r="A14" s="1" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
@@ -4388,25 +4196,25 @@
     </row>
     <row r="15" spans="1:26">
       <c r="A15" s="1" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
@@ -4430,31 +4238,31 @@
     </row>
     <row r="16" spans="1:26">
       <c r="A16" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="H16" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="I16" s="1" t="s">
         <v>162</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>169</v>
       </c>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
@@ -4476,13 +4284,13 @@
     </row>
     <row r="17" spans="1:26">
       <c r="A17" s="1" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
@@ -4510,16 +4318,16 @@
     </row>
     <row r="18" spans="1:26">
       <c r="A18" s="1" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
@@ -4546,3884 +4354,3884 @@
     </row>
     <row r="19" spans="1:26">
       <c r="A19" s="5" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="B19" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="C19" t="s">
+        <v>171</v>
+      </c>
+      <c r="D19" t="s">
+        <v>172</v>
+      </c>
+      <c r="E19" t="s">
+        <v>173</v>
+      </c>
+      <c r="F19" t="s">
+        <v>174</v>
+      </c>
+      <c r="G19" t="s">
+        <v>175</v>
+      </c>
+      <c r="H19" t="s">
+        <v>176</v>
+      </c>
+      <c r="I19" t="s">
         <v>177</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="20" spans="1:26">
       <c r="A20" s="5" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="D20" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="C20" t="s">
         <v>179</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="D20" t="s">
+        <v>172</v>
+      </c>
+      <c r="E20" t="s">
+        <v>174</v>
+      </c>
+      <c r="F20" t="s">
+        <v>177</v>
+      </c>
+      <c r="G20" t="s">
+        <v>175</v>
+      </c>
+      <c r="H20" t="s">
+        <v>176</v>
+      </c>
+      <c r="I20" t="s">
+        <v>180</v>
+      </c>
+      <c r="J20" t="s">
         <v>181</v>
       </c>
-      <c r="F20" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="G20" s="7" t="s">
+      <c r="K20" t="s">
         <v>182</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="I20" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="J20" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="K20" s="7" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="21" spans="1:26">
       <c r="A21" s="5" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="D21" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="C21" t="s">
+        <v>172</v>
+      </c>
+      <c r="D21" t="s">
+        <v>173</v>
+      </c>
+      <c r="E21" t="s">
+        <v>174</v>
+      </c>
+      <c r="F21" t="s">
+        <v>175</v>
+      </c>
+      <c r="G21" t="s">
+        <v>176</v>
+      </c>
+      <c r="H21" t="s">
+        <v>177</v>
+      </c>
+      <c r="I21" t="s">
         <v>180</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="J21" t="s">
         <v>181</v>
       </c>
-      <c r="F21" s="7" t="s">
+      <c r="K21" t="s">
         <v>182</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="I21" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="J21" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="K21" s="7" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="22" spans="1:26">
       <c r="A22" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="H22" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="I22" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="J22" s="7" t="s">
-        <v>194</v>
+        <v>184</v>
+      </c>
+      <c r="C22" t="s">
+        <v>172</v>
+      </c>
+      <c r="D22" t="s">
+        <v>173</v>
+      </c>
+      <c r="E22" t="s">
+        <v>174</v>
+      </c>
+      <c r="F22" t="s">
+        <v>175</v>
+      </c>
+      <c r="G22" t="s">
+        <v>176</v>
+      </c>
+      <c r="H22" t="s">
+        <v>185</v>
+      </c>
+      <c r="I22" t="s">
+        <v>186</v>
+      </c>
+      <c r="J22" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="23" spans="1:26">
       <c r="A23" s="5" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>201</v>
+        <v>188</v>
+      </c>
+      <c r="C23" t="s">
+        <v>189</v>
+      </c>
+      <c r="D23" t="s">
+        <v>190</v>
+      </c>
+      <c r="E23" t="s">
+        <v>191</v>
+      </c>
+      <c r="F23" t="s">
+        <v>192</v>
+      </c>
+      <c r="G23" t="s">
+        <v>193</v>
+      </c>
+      <c r="H23" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="24" spans="1:26">
       <c r="A24" s="5" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="G24" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="H24" s="7" t="s">
-        <v>201</v>
+        <v>195</v>
+      </c>
+      <c r="C24" t="s">
+        <v>189</v>
+      </c>
+      <c r="D24" t="s">
+        <v>190</v>
+      </c>
+      <c r="E24" t="s">
+        <v>191</v>
+      </c>
+      <c r="F24" t="s">
+        <v>192</v>
+      </c>
+      <c r="G24" t="s">
+        <v>193</v>
+      </c>
+      <c r="H24" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="25" spans="1:26">
       <c r="A25" s="5" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="H25" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="I25" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="J25" s="7" t="s">
-        <v>208</v>
+        <v>196</v>
+      </c>
+      <c r="C25" t="s">
+        <v>197</v>
+      </c>
+      <c r="D25" t="s">
+        <v>198</v>
+      </c>
+      <c r="E25" t="s">
+        <v>199</v>
+      </c>
+      <c r="F25" t="s">
+        <v>175</v>
+      </c>
+      <c r="G25" t="s">
+        <v>176</v>
+      </c>
+      <c r="H25" t="s">
+        <v>174</v>
+      </c>
+      <c r="I25" t="s">
+        <v>200</v>
+      </c>
+      <c r="J25" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="26" spans="1:26">
       <c r="A26" s="5" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="C26" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="C26" t="s">
+        <v>197</v>
+      </c>
+      <c r="D26" t="s">
+        <v>203</v>
+      </c>
+      <c r="E26" t="s">
         <v>204</v>
       </c>
-      <c r="D26" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="G26" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="H26" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="I26" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="J26" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="K26" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="L26" s="7" t="s">
+      <c r="F26" t="s">
+        <v>205</v>
+      </c>
+      <c r="G26" t="s">
+        <v>206</v>
+      </c>
+      <c r="H26" t="s">
         <v>207</v>
       </c>
-      <c r="M26" s="7" t="s">
+      <c r="I26" t="s">
+        <v>175</v>
+      </c>
+      <c r="J26" t="s">
+        <v>176</v>
+      </c>
+      <c r="K26" t="s">
         <v>208</v>
+      </c>
+      <c r="L26" t="s">
+        <v>200</v>
+      </c>
+      <c r="M26" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="27" spans="1:26">
       <c r="A27" s="5" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="C27" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="C27" t="s">
+        <v>197</v>
+      </c>
+      <c r="D27" t="s">
+        <v>203</v>
+      </c>
+      <c r="E27" t="s">
         <v>204</v>
       </c>
-      <c r="D27" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="H27" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="I27" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="J27" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="K27" s="7" t="s">
+      <c r="F27" t="s">
+        <v>206</v>
+      </c>
+      <c r="G27" t="s">
         <v>207</v>
       </c>
-      <c r="L27" s="7" t="s">
+      <c r="H27" t="s">
+        <v>175</v>
+      </c>
+      <c r="I27" t="s">
+        <v>176</v>
+      </c>
+      <c r="J27" t="s">
         <v>208</v>
+      </c>
+      <c r="K27" t="s">
+        <v>200</v>
+      </c>
+      <c r="L27" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="28" spans="1:26">
       <c r="A28" s="5" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="G28" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="H28" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="I28" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="J28" s="7" t="s">
-        <v>222</v>
-      </c>
-      <c r="K28" s="7" t="s">
-        <v>208</v>
+        <v>210</v>
+      </c>
+      <c r="C28" t="s">
+        <v>211</v>
+      </c>
+      <c r="D28" t="s">
+        <v>212</v>
+      </c>
+      <c r="E28" t="s">
+        <v>174</v>
+      </c>
+      <c r="F28" t="s">
+        <v>175</v>
+      </c>
+      <c r="G28" t="s">
+        <v>176</v>
+      </c>
+      <c r="H28" t="s">
+        <v>213</v>
+      </c>
+      <c r="I28" t="s">
+        <v>214</v>
+      </c>
+      <c r="J28" t="s">
+        <v>215</v>
+      </c>
+      <c r="K28" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="29" spans="1:26">
       <c r="A29" s="5" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="H29" s="7" t="s">
-        <v>226</v>
-      </c>
-      <c r="I29" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="J29" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="K29" s="7" t="s">
-        <v>222</v>
-      </c>
-      <c r="L29" s="7" t="s">
-        <v>208</v>
+        <v>216</v>
+      </c>
+      <c r="C29" t="s">
+        <v>172</v>
+      </c>
+      <c r="D29" t="s">
+        <v>173</v>
+      </c>
+      <c r="E29" t="s">
+        <v>174</v>
+      </c>
+      <c r="F29" t="s">
+        <v>217</v>
+      </c>
+      <c r="G29" t="s">
+        <v>218</v>
+      </c>
+      <c r="H29" t="s">
+        <v>219</v>
+      </c>
+      <c r="I29" t="s">
+        <v>220</v>
+      </c>
+      <c r="J29" t="s">
+        <v>221</v>
+      </c>
+      <c r="K29" t="s">
+        <v>215</v>
+      </c>
+      <c r="L29" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="30" spans="1:26">
       <c r="A30" s="5" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="F30" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="G30" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="H30" s="7" t="s">
-        <v>233</v>
+        <v>222</v>
+      </c>
+      <c r="C30" t="s">
+        <v>223</v>
+      </c>
+      <c r="D30" t="s">
+        <v>224</v>
+      </c>
+      <c r="E30" t="s">
+        <v>173</v>
+      </c>
+      <c r="F30" t="s">
+        <v>174</v>
+      </c>
+      <c r="G30" t="s">
+        <v>225</v>
+      </c>
+      <c r="H30" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="31" spans="1:26">
       <c r="A31" s="5" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B31" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="C31" t="s">
+        <v>172</v>
+      </c>
+      <c r="D31" t="s">
+        <v>173</v>
+      </c>
+      <c r="E31" t="s">
+        <v>174</v>
+      </c>
+      <c r="F31" t="s">
+        <v>217</v>
+      </c>
+      <c r="G31" t="s">
+        <v>218</v>
+      </c>
+      <c r="H31" t="s">
+        <v>220</v>
+      </c>
+      <c r="I31" t="s">
+        <v>221</v>
+      </c>
+      <c r="J31" t="s">
+        <v>215</v>
+      </c>
+      <c r="K31" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="32" spans="1:26">
+      <c r="A32" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="C32" t="s">
+        <v>229</v>
+      </c>
+      <c r="D32" t="s">
+        <v>230</v>
+      </c>
+      <c r="E32" t="s">
+        <v>231</v>
+      </c>
+      <c r="F32" t="s">
+        <v>232</v>
+      </c>
+      <c r="G32" t="s">
+        <v>233</v>
+      </c>
+      <c r="H32" t="s">
         <v>234</v>
       </c>
-      <c r="C31" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="G31" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="H31" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="I31" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="J31" s="7" t="s">
-        <v>222</v>
-      </c>
-      <c r="K31" s="7" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="32" spans="1:26">
-      <c r="A32" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="B32" s="9" t="s">
+      <c r="I32" t="s">
         <v>235</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="J32" t="s">
         <v>236</v>
       </c>
-      <c r="D32" s="7" t="s">
+      <c r="K32" t="s">
         <v>237</v>
       </c>
-      <c r="E32" s="7" t="s">
+      <c r="L32" t="s">
         <v>238</v>
-      </c>
-      <c r="F32" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="G32" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="H32" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="I32" s="7" t="s">
-        <v>242</v>
-      </c>
-      <c r="J32" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="K32" s="7" t="s">
-        <v>244</v>
-      </c>
-      <c r="L32" s="7" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="33" spans="1:17">
       <c r="A33" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B33" s="9" t="s">
-        <v>246</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="E33" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33" s="8" t="s">
         <v>239</v>
       </c>
-      <c r="F33" s="7" t="s">
+      <c r="C33" t="s">
         <v>240</v>
       </c>
-      <c r="G33" s="7" t="s">
+      <c r="D33" t="s">
         <v>241</v>
       </c>
-      <c r="H33" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="I33" s="7" t="s">
+      <c r="E33" t="s">
+        <v>232</v>
+      </c>
+      <c r="F33" t="s">
+        <v>233</v>
+      </c>
+      <c r="G33" t="s">
+        <v>234</v>
+      </c>
+      <c r="H33" t="s">
         <v>242</v>
       </c>
-      <c r="J33" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="K33" s="7" t="s">
-        <v>244</v>
-      </c>
-      <c r="L33" s="7" t="s">
-        <v>245</v>
+      <c r="I33" t="s">
+        <v>235</v>
+      </c>
+      <c r="J33" t="s">
+        <v>236</v>
+      </c>
+      <c r="K33" t="s">
+        <v>237</v>
+      </c>
+      <c r="L33" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="34" spans="1:17">
       <c r="A34" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B34" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="F34" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="C34" t="s">
         <v>240</v>
       </c>
-      <c r="G34" s="7" t="s">
+      <c r="D34" t="s">
         <v>241</v>
       </c>
-      <c r="H34" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="I34" s="7" t="s">
+      <c r="E34" t="s">
+        <v>232</v>
+      </c>
+      <c r="F34" t="s">
+        <v>233</v>
+      </c>
+      <c r="G34" t="s">
+        <v>234</v>
+      </c>
+      <c r="H34" t="s">
         <v>242</v>
       </c>
-      <c r="J34" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="K34" s="7" t="s">
-        <v>244</v>
-      </c>
-      <c r="L34" s="7" t="s">
-        <v>245</v>
+      <c r="I34" t="s">
+        <v>235</v>
+      </c>
+      <c r="J34" t="s">
+        <v>236</v>
+      </c>
+      <c r="K34" t="s">
+        <v>237</v>
+      </c>
+      <c r="L34" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="35" spans="1:17">
       <c r="A35" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B35" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="C35" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="C35" t="s">
+        <v>229</v>
+      </c>
+      <c r="D35" t="s">
+        <v>230</v>
+      </c>
+      <c r="E35" t="s">
+        <v>245</v>
+      </c>
+      <c r="F35" t="s">
+        <v>232</v>
+      </c>
+      <c r="G35" t="s">
+        <v>233</v>
+      </c>
+      <c r="H35" t="s">
+        <v>234</v>
+      </c>
+      <c r="I35" t="s">
+        <v>235</v>
+      </c>
+      <c r="J35" t="s">
         <v>236</v>
       </c>
-      <c r="D35" s="7" t="s">
+      <c r="K35" t="s">
         <v>237</v>
       </c>
-      <c r="E35" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="F35" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="G35" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="H35" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="I35" s="7" t="s">
-        <v>242</v>
-      </c>
-      <c r="J35" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="K35" s="7" t="s">
-        <v>244</v>
-      </c>
-      <c r="L35" s="7" t="s">
-        <v>245</v>
-      </c>
-      <c r="M35" s="7" t="s">
-        <v>253</v>
+      <c r="L35" t="s">
+        <v>238</v>
+      </c>
+      <c r="M35" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="36" spans="1:17">
       <c r="A36" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B36" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="C36" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="C36" t="s">
+        <v>229</v>
+      </c>
+      <c r="D36" t="s">
+        <v>230</v>
+      </c>
+      <c r="E36" t="s">
+        <v>245</v>
+      </c>
+      <c r="F36" t="s">
+        <v>232</v>
+      </c>
+      <c r="G36" t="s">
+        <v>233</v>
+      </c>
+      <c r="H36" t="s">
+        <v>234</v>
+      </c>
+      <c r="I36" t="s">
+        <v>235</v>
+      </c>
+      <c r="J36" t="s">
         <v>236</v>
       </c>
-      <c r="D36" s="7" t="s">
+      <c r="K36" t="s">
         <v>237</v>
       </c>
-      <c r="E36" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="F36" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="G36" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="H36" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="I36" s="7" t="s">
-        <v>242</v>
-      </c>
-      <c r="J36" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="K36" s="7" t="s">
-        <v>244</v>
-      </c>
-      <c r="L36" s="7" t="s">
-        <v>245</v>
+      <c r="L36" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="37" spans="1:17">
       <c r="A37" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B37" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="C37" t="s">
+        <v>240</v>
+      </c>
+      <c r="D37" t="s">
+        <v>241</v>
+      </c>
+      <c r="E37" t="s">
+        <v>232</v>
+      </c>
+      <c r="F37" t="s">
+        <v>234</v>
+      </c>
+      <c r="G37" t="s">
+        <v>242</v>
+      </c>
+      <c r="H37" t="s">
+        <v>235</v>
+      </c>
+      <c r="I37" t="s">
+        <v>236</v>
+      </c>
+      <c r="J37" t="s">
+        <v>237</v>
+      </c>
+      <c r="K37" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17">
+      <c r="A38" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="C38" t="s">
+        <v>250</v>
+      </c>
+      <c r="D38" t="s">
+        <v>251</v>
+      </c>
+      <c r="E38" t="s">
+        <v>252</v>
+      </c>
+      <c r="F38" t="s">
+        <v>203</v>
+      </c>
+      <c r="G38" t="s">
+        <v>253</v>
+      </c>
+      <c r="H38" t="s">
+        <v>254</v>
+      </c>
+      <c r="I38" t="s">
+        <v>204</v>
+      </c>
+      <c r="J38" t="s">
         <v>255</v>
       </c>
-      <c r="C37" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="F37" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="G37" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="H37" s="7" t="s">
-        <v>242</v>
-      </c>
-      <c r="I37" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="J37" s="7" t="s">
-        <v>244</v>
-      </c>
-      <c r="K37" s="7" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17">
-      <c r="A38" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="B38" s="6" t="s">
+      <c r="K38" t="s">
         <v>256</v>
       </c>
-      <c r="C38" s="7" t="s">
+      <c r="L38" t="s">
         <v>257</v>
       </c>
-      <c r="D38" s="7" t="s">
+      <c r="M38" t="s">
+        <v>180</v>
+      </c>
+      <c r="N38" t="s">
         <v>258</v>
       </c>
-      <c r="E38" s="7" t="s">
+      <c r="O38" t="s">
         <v>259</v>
       </c>
-      <c r="F38" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="G38" s="7" t="s">
+      <c r="P38" t="s">
         <v>260</v>
       </c>
-      <c r="H38" s="7" t="s">
+      <c r="Q38" t="s">
         <v>261</v>
-      </c>
-      <c r="I38" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="J38" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="K38" s="7" t="s">
-        <v>263</v>
-      </c>
-      <c r="L38" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="M38" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="N38" s="7" t="s">
-        <v>265</v>
-      </c>
-      <c r="O38" s="7" t="s">
-        <v>266</v>
-      </c>
-      <c r="P38" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="Q38" s="7" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="39" spans="1:17">
       <c r="A39" s="5" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="B39" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="C39" t="s">
+        <v>250</v>
+      </c>
+      <c r="D39" t="s">
+        <v>263</v>
+      </c>
+      <c r="E39" t="s">
+        <v>264</v>
+      </c>
+      <c r="F39" t="s">
+        <v>265</v>
+      </c>
+      <c r="G39" t="s">
+        <v>266</v>
+      </c>
+      <c r="H39" t="s">
+        <v>267</v>
+      </c>
+      <c r="I39" t="s">
+        <v>268</v>
+      </c>
+      <c r="J39" t="s">
         <v>269</v>
       </c>
-      <c r="C39" s="7" t="s">
-        <v>257</v>
-      </c>
-      <c r="D39" s="7" t="s">
+      <c r="K39" t="s">
         <v>270</v>
       </c>
-      <c r="E39" s="7" t="s">
+      <c r="L39" t="s">
         <v>271</v>
       </c>
-      <c r="F39" s="7" t="s">
+      <c r="M39" t="s">
         <v>272</v>
       </c>
-      <c r="G39" s="7" t="s">
+      <c r="N39" t="s">
         <v>273</v>
       </c>
-      <c r="H39" s="7" t="s">
+      <c r="O39" t="s">
         <v>274</v>
       </c>
-      <c r="I39" s="7" t="s">
+      <c r="P39" t="s">
         <v>275</v>
-      </c>
-      <c r="J39" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="K39" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="L39" s="7" t="s">
-        <v>278</v>
-      </c>
-      <c r="M39" s="7" t="s">
-        <v>279</v>
-      </c>
-      <c r="N39" s="7" t="s">
-        <v>280</v>
-      </c>
-      <c r="O39" s="7" t="s">
-        <v>281</v>
-      </c>
-      <c r="P39" s="7" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="40" spans="1:17">
       <c r="A40" s="5" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>283</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="E40" s="7" t="s">
-        <v>257</v>
-      </c>
-      <c r="F40" s="7" t="s">
-        <v>187</v>
+        <v>276</v>
+      </c>
+      <c r="C40" t="s">
+        <v>217</v>
+      </c>
+      <c r="D40" t="s">
+        <v>251</v>
+      </c>
+      <c r="E40" t="s">
+        <v>250</v>
+      </c>
+      <c r="F40" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="41" spans="1:17">
       <c r="A41" s="5" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>257</v>
-      </c>
-      <c r="E41" s="7" t="s">
-        <v>285</v>
+        <v>277</v>
+      </c>
+      <c r="C41" t="s">
+        <v>217</v>
+      </c>
+      <c r="D41" t="s">
+        <v>250</v>
+      </c>
+      <c r="E41" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="42" spans="1:17">
       <c r="A42" s="5" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="D42" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="E42" s="7" t="s">
-        <v>257</v>
+        <v>279</v>
+      </c>
+      <c r="C42" t="s">
+        <v>217</v>
+      </c>
+      <c r="D42" t="s">
+        <v>278</v>
+      </c>
+      <c r="E42" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="43" spans="1:17">
       <c r="A43" s="5" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="D43" s="7" t="s">
-        <v>257</v>
-      </c>
-      <c r="E43" s="7" t="s">
-        <v>285</v>
+        <v>280</v>
+      </c>
+      <c r="C43" t="s">
+        <v>217</v>
+      </c>
+      <c r="D43" t="s">
+        <v>250</v>
+      </c>
+      <c r="E43" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="44" spans="1:17">
       <c r="A44" s="5" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="C44" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="D44" s="7" t="s">
-        <v>257</v>
-      </c>
-      <c r="E44" s="7" t="s">
-        <v>289</v>
+        <v>281</v>
+      </c>
+      <c r="C44" t="s">
+        <v>217</v>
+      </c>
+      <c r="D44" t="s">
+        <v>250</v>
+      </c>
+      <c r="E44" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="45" spans="1:17">
       <c r="A45" s="5" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>290</v>
-      </c>
-      <c r="C45" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="D45" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="E45" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="F45" s="7" t="s">
-        <v>291</v>
-      </c>
-      <c r="G45" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="H45" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="I45" s="7" t="s">
-        <v>292</v>
-      </c>
-      <c r="J45" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="K45" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="L45" s="7" t="s">
-        <v>295</v>
+        <v>283</v>
+      </c>
+      <c r="C45" t="s">
+        <v>172</v>
+      </c>
+      <c r="D45" t="s">
+        <v>173</v>
+      </c>
+      <c r="E45" t="s">
+        <v>174</v>
+      </c>
+      <c r="F45" t="s">
+        <v>284</v>
+      </c>
+      <c r="G45" t="s">
+        <v>175</v>
+      </c>
+      <c r="H45" t="s">
+        <v>176</v>
+      </c>
+      <c r="I45" t="s">
+        <v>285</v>
+      </c>
+      <c r="J45" t="s">
+        <v>286</v>
+      </c>
+      <c r="K45" t="s">
+        <v>287</v>
+      </c>
+      <c r="L45" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="46" spans="1:17">
       <c r="A46" s="5" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>296</v>
-      </c>
-      <c r="C46" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="D46" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="E46" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="F46" s="7" t="s">
-        <v>291</v>
-      </c>
-      <c r="G46" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="H46" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="I46" s="7" t="s">
-        <v>292</v>
-      </c>
-      <c r="J46" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="K46" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="L46" s="7" t="s">
-        <v>295</v>
+        <v>289</v>
+      </c>
+      <c r="C46" t="s">
+        <v>172</v>
+      </c>
+      <c r="D46" t="s">
+        <v>173</v>
+      </c>
+      <c r="E46" t="s">
+        <v>174</v>
+      </c>
+      <c r="F46" t="s">
+        <v>284</v>
+      </c>
+      <c r="G46" t="s">
+        <v>175</v>
+      </c>
+      <c r="H46" t="s">
+        <v>176</v>
+      </c>
+      <c r="I46" t="s">
+        <v>285</v>
+      </c>
+      <c r="J46" t="s">
+        <v>286</v>
+      </c>
+      <c r="K46" t="s">
+        <v>287</v>
+      </c>
+      <c r="L46" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="47" spans="1:17">
       <c r="A47" s="5" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>297</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="D47" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="E47" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="F47" s="7" t="s">
-        <v>291</v>
-      </c>
-      <c r="G47" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="H47" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="I47" s="7" t="s">
-        <v>292</v>
-      </c>
-      <c r="J47" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="K47" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="L47" s="7" t="s">
-        <v>295</v>
+        <v>290</v>
+      </c>
+      <c r="C47" t="s">
+        <v>172</v>
+      </c>
+      <c r="D47" t="s">
+        <v>173</v>
+      </c>
+      <c r="E47" t="s">
+        <v>174</v>
+      </c>
+      <c r="F47" t="s">
+        <v>284</v>
+      </c>
+      <c r="G47" t="s">
+        <v>175</v>
+      </c>
+      <c r="H47" t="s">
+        <v>176</v>
+      </c>
+      <c r="I47" t="s">
+        <v>285</v>
+      </c>
+      <c r="J47" t="s">
+        <v>286</v>
+      </c>
+      <c r="K47" t="s">
+        <v>287</v>
+      </c>
+      <c r="L47" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="48" spans="1:17">
       <c r="A48" s="5" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>298</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="D48" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="E48" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="F48" s="7" t="s">
         <v>291</v>
       </c>
-      <c r="G48" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="H48" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="I48" s="7" t="s">
-        <v>292</v>
-      </c>
-      <c r="J48" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="K48" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="L48" s="7" t="s">
-        <v>295</v>
+      <c r="C48" t="s">
+        <v>172</v>
+      </c>
+      <c r="D48" t="s">
+        <v>173</v>
+      </c>
+      <c r="E48" t="s">
+        <v>174</v>
+      </c>
+      <c r="F48" t="s">
+        <v>284</v>
+      </c>
+      <c r="G48" t="s">
+        <v>175</v>
+      </c>
+      <c r="H48" t="s">
+        <v>176</v>
+      </c>
+      <c r="I48" t="s">
+        <v>285</v>
+      </c>
+      <c r="J48" t="s">
+        <v>286</v>
+      </c>
+      <c r="K48" t="s">
+        <v>287</v>
+      </c>
+      <c r="L48" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="49" spans="1:13">
       <c r="A49" s="5" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>299</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="D49" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="E49" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="F49" s="7" t="s">
-        <v>291</v>
-      </c>
-      <c r="G49" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="H49" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="I49" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="J49" s="7" t="s">
+      <c r="C49" t="s">
+        <v>172</v>
+      </c>
+      <c r="D49" t="s">
+        <v>173</v>
+      </c>
+      <c r="E49" t="s">
+        <v>174</v>
+      </c>
+      <c r="F49" t="s">
+        <v>284</v>
+      </c>
+      <c r="G49" t="s">
+        <v>175</v>
+      </c>
+      <c r="H49" t="s">
+        <v>176</v>
+      </c>
+      <c r="I49" t="s">
+        <v>285</v>
+      </c>
+      <c r="J49" t="s">
+        <v>286</v>
+      </c>
+      <c r="K49" t="s">
+        <v>287</v>
+      </c>
+      <c r="L49" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13">
+      <c r="A50" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B50" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="K49" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="L49" s="7" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13">
-      <c r="A50" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>300</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="D50" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="E50" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="F50" s="7" t="s">
-        <v>291</v>
-      </c>
-      <c r="G50" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="H50" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="I50" s="7" t="s">
-        <v>292</v>
-      </c>
-      <c r="J50" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="K50" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="L50" s="7" t="s">
-        <v>295</v>
+      <c r="C50" t="s">
+        <v>172</v>
+      </c>
+      <c r="D50" t="s">
+        <v>173</v>
+      </c>
+      <c r="E50" t="s">
+        <v>174</v>
+      </c>
+      <c r="F50" t="s">
+        <v>284</v>
+      </c>
+      <c r="G50" t="s">
+        <v>175</v>
+      </c>
+      <c r="H50" t="s">
+        <v>176</v>
+      </c>
+      <c r="I50" t="s">
+        <v>285</v>
+      </c>
+      <c r="J50" t="s">
+        <v>286</v>
+      </c>
+      <c r="K50" t="s">
+        <v>287</v>
+      </c>
+      <c r="L50" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="51" spans="1:13">
       <c r="A51" s="5" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="B51" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="C51" t="s">
+        <v>295</v>
+      </c>
+      <c r="D51" t="s">
+        <v>296</v>
+      </c>
+      <c r="E51" t="s">
+        <v>297</v>
+      </c>
+      <c r="F51" t="s">
+        <v>298</v>
+      </c>
+      <c r="G51" t="s">
+        <v>251</v>
+      </c>
+      <c r="H51" t="s">
+        <v>299</v>
+      </c>
+      <c r="I51" t="s">
+        <v>300</v>
+      </c>
+      <c r="J51" t="s">
         <v>301</v>
       </c>
-      <c r="C51" s="7" t="s">
+      <c r="K51" t="s">
         <v>302</v>
       </c>
-      <c r="D51" s="7" t="s">
+      <c r="L51" t="s">
         <v>303</v>
       </c>
-      <c r="E51" s="7" t="s">
+      <c r="M51" t="s">
         <v>304</v>
-      </c>
-      <c r="F51" s="7" t="s">
-        <v>305</v>
-      </c>
-      <c r="G51" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="H51" s="7" t="s">
-        <v>306</v>
-      </c>
-      <c r="I51" s="7" t="s">
-        <v>307</v>
-      </c>
-      <c r="J51" s="7" t="s">
-        <v>308</v>
-      </c>
-      <c r="K51" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="L51" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="M51" s="7" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="52" spans="1:13">
       <c r="A52" s="5" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>312</v>
-      </c>
-      <c r="C52" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="D52" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="C52" t="s">
+        <v>172</v>
+      </c>
+      <c r="D52" t="s">
+        <v>173</v>
+      </c>
+      <c r="E52" t="s">
+        <v>174</v>
+      </c>
+      <c r="F52" t="s">
+        <v>175</v>
+      </c>
+      <c r="G52" t="s">
+        <v>176</v>
+      </c>
+      <c r="H52" t="s">
+        <v>306</v>
+      </c>
+      <c r="I52" t="s">
+        <v>307</v>
+      </c>
+      <c r="J52" t="s">
         <v>180</v>
-      </c>
-      <c r="E52" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="F52" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="G52" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="H52" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="I52" s="7" t="s">
-        <v>314</v>
-      </c>
-      <c r="J52" s="7" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="53" spans="1:13">
       <c r="A53" s="5" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>315</v>
-      </c>
-      <c r="C53" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="D53" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="C53" t="s">
+        <v>172</v>
+      </c>
+      <c r="D53" t="s">
+        <v>173</v>
+      </c>
+      <c r="E53" t="s">
+        <v>174</v>
+      </c>
+      <c r="F53" t="s">
+        <v>175</v>
+      </c>
+      <c r="G53" t="s">
+        <v>176</v>
+      </c>
+      <c r="H53" t="s">
+        <v>306</v>
+      </c>
+      <c r="I53" t="s">
+        <v>307</v>
+      </c>
+      <c r="J53" t="s">
         <v>180</v>
-      </c>
-      <c r="E53" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="F53" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="G53" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="H53" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="I53" s="7" t="s">
-        <v>314</v>
-      </c>
-      <c r="J53" s="7" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="54" spans="1:13">
       <c r="A54" s="5" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>316</v>
-      </c>
-      <c r="C54" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="D54" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="E54" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="F54" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="G54" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="H54" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="I54" s="7" t="s">
-        <v>314</v>
-      </c>
-      <c r="J54" s="7" t="s">
-        <v>187</v>
+        <v>309</v>
+      </c>
+      <c r="C54" t="s">
+        <v>217</v>
+      </c>
+      <c r="D54" t="s">
+        <v>218</v>
+      </c>
+      <c r="E54" t="s">
+        <v>306</v>
+      </c>
+      <c r="F54" t="s">
+        <v>175</v>
+      </c>
+      <c r="G54" t="s">
+        <v>176</v>
+      </c>
+      <c r="H54" t="s">
+        <v>251</v>
+      </c>
+      <c r="I54" t="s">
+        <v>307</v>
+      </c>
+      <c r="J54" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="55" spans="1:13">
       <c r="A55" s="5" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>317</v>
-      </c>
-      <c r="C55" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="D55" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="E55" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="F55" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="G55" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="H55" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="I55" s="7" t="s">
-        <v>314</v>
-      </c>
-      <c r="J55" s="7" t="s">
-        <v>187</v>
+        <v>310</v>
+      </c>
+      <c r="C55" t="s">
+        <v>217</v>
+      </c>
+      <c r="D55" t="s">
+        <v>218</v>
+      </c>
+      <c r="E55" t="s">
+        <v>306</v>
+      </c>
+      <c r="F55" t="s">
+        <v>175</v>
+      </c>
+      <c r="G55" t="s">
+        <v>176</v>
+      </c>
+      <c r="H55" t="s">
+        <v>278</v>
+      </c>
+      <c r="I55" t="s">
+        <v>307</v>
+      </c>
+      <c r="J55" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="56" spans="1:13">
       <c r="A56" s="5" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>318</v>
-      </c>
-      <c r="C56" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="D56" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="E56" s="7" t="s">
-        <v>319</v>
-      </c>
-      <c r="F56" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="C56" t="s">
+        <v>217</v>
+      </c>
+      <c r="D56" t="s">
+        <v>218</v>
+      </c>
+      <c r="E56" t="s">
+        <v>312</v>
+      </c>
+      <c r="F56" t="s">
+        <v>306</v>
+      </c>
+      <c r="G56" t="s">
+        <v>175</v>
+      </c>
+      <c r="H56" t="s">
+        <v>176</v>
+      </c>
+      <c r="I56" t="s">
         <v>313</v>
       </c>
-      <c r="G56" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="H56" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="I56" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="J56" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="K56" s="7" t="s">
-        <v>314</v>
-      </c>
-      <c r="L56" s="7" t="s">
-        <v>187</v>
+      <c r="J56" t="s">
+        <v>278</v>
+      </c>
+      <c r="K56" t="s">
+        <v>307</v>
+      </c>
+      <c r="L56" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="57" spans="1:13">
       <c r="A57" s="5" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C57" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="D57" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="E57" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="F57" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G57" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="H57" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="I57" s="7" t="s">
         <v>314</v>
       </c>
-      <c r="J57" s="7" t="s">
-        <v>187</v>
+      <c r="C57" t="s">
+        <v>217</v>
+      </c>
+      <c r="D57" t="s">
+        <v>175</v>
+      </c>
+      <c r="E57" t="s">
+        <v>176</v>
+      </c>
+      <c r="F57" t="s">
+        <v>218</v>
+      </c>
+      <c r="G57" t="s">
+        <v>306</v>
+      </c>
+      <c r="H57" t="s">
+        <v>278</v>
+      </c>
+      <c r="I57" t="s">
+        <v>307</v>
+      </c>
+      <c r="J57" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="58" spans="1:13">
       <c r="A58" s="5" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="C58" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="D58" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="E58" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="F58" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="G58" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="H58" s="7" t="s">
-        <v>324</v>
-      </c>
-      <c r="I58" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="J58" s="7" t="s">
-        <v>314</v>
-      </c>
-      <c r="K58" s="7" t="s">
-        <v>187</v>
+        <v>315</v>
+      </c>
+      <c r="C58" t="s">
+        <v>217</v>
+      </c>
+      <c r="D58" t="s">
+        <v>218</v>
+      </c>
+      <c r="E58" t="s">
+        <v>175</v>
+      </c>
+      <c r="F58" t="s">
+        <v>176</v>
+      </c>
+      <c r="G58" t="s">
+        <v>316</v>
+      </c>
+      <c r="H58" t="s">
+        <v>317</v>
+      </c>
+      <c r="I58" t="s">
+        <v>278</v>
+      </c>
+      <c r="J58" t="s">
+        <v>307</v>
+      </c>
+      <c r="K58" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="59" spans="1:13">
       <c r="A59" s="5" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>325</v>
-      </c>
-      <c r="C59" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="D59" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="E59" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="F59" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="G59" s="7" t="s">
-        <v>326</v>
-      </c>
-      <c r="H59" s="7" t="s">
-        <v>327</v>
-      </c>
-      <c r="I59" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="J59" s="7" t="s">
-        <v>314</v>
-      </c>
-      <c r="K59" s="7" t="s">
-        <v>187</v>
+        <v>318</v>
+      </c>
+      <c r="C59" t="s">
+        <v>217</v>
+      </c>
+      <c r="D59" t="s">
+        <v>218</v>
+      </c>
+      <c r="E59" t="s">
+        <v>175</v>
+      </c>
+      <c r="F59" t="s">
+        <v>176</v>
+      </c>
+      <c r="G59" t="s">
+        <v>319</v>
+      </c>
+      <c r="H59" t="s">
+        <v>320</v>
+      </c>
+      <c r="I59" t="s">
+        <v>278</v>
+      </c>
+      <c r="J59" t="s">
+        <v>307</v>
+      </c>
+      <c r="K59" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="60" spans="1:13">
       <c r="A60" s="5" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="C60" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="D60" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="E60" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="F60" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="G60" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="H60" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="I60" s="7" t="s">
-        <v>330</v>
-      </c>
-      <c r="J60" s="7" t="s">
-        <v>331</v>
+        <v>321</v>
+      </c>
+      <c r="C60" t="s">
+        <v>172</v>
+      </c>
+      <c r="D60" t="s">
+        <v>173</v>
+      </c>
+      <c r="E60" t="s">
+        <v>174</v>
+      </c>
+      <c r="F60" t="s">
+        <v>175</v>
+      </c>
+      <c r="G60" t="s">
+        <v>176</v>
+      </c>
+      <c r="H60" t="s">
+        <v>322</v>
+      </c>
+      <c r="I60" t="s">
+        <v>323</v>
+      </c>
+      <c r="J60" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="61" spans="1:13">
       <c r="A61" s="5" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>332</v>
-      </c>
-      <c r="C61" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="D61" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="E61" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="F61" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="G61" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="H61" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="I61" s="7" t="s">
-        <v>330</v>
-      </c>
-      <c r="J61" s="7" t="s">
-        <v>331</v>
+        <v>325</v>
+      </c>
+      <c r="C61" t="s">
+        <v>172</v>
+      </c>
+      <c r="D61" t="s">
+        <v>173</v>
+      </c>
+      <c r="E61" t="s">
+        <v>174</v>
+      </c>
+      <c r="F61" t="s">
+        <v>175</v>
+      </c>
+      <c r="G61" t="s">
+        <v>176</v>
+      </c>
+      <c r="H61" t="s">
+        <v>322</v>
+      </c>
+      <c r="I61" t="s">
+        <v>323</v>
+      </c>
+      <c r="J61" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="62" spans="1:13">
       <c r="A62" s="5" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>333</v>
-      </c>
-      <c r="C62" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="D62" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="E62" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="F62" s="7" t="s">
-        <v>334</v>
-      </c>
-      <c r="G62" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="H62" s="7" t="s">
-        <v>335</v>
-      </c>
-      <c r="I62" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="J62" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="K62" s="7" t="s">
-        <v>183</v>
+        <v>326</v>
+      </c>
+      <c r="C62" t="s">
+        <v>172</v>
+      </c>
+      <c r="D62" t="s">
+        <v>173</v>
+      </c>
+      <c r="E62" t="s">
+        <v>174</v>
+      </c>
+      <c r="F62" t="s">
+        <v>327</v>
+      </c>
+      <c r="G62" t="s">
+        <v>322</v>
+      </c>
+      <c r="H62" t="s">
+        <v>328</v>
+      </c>
+      <c r="I62" t="s">
+        <v>324</v>
+      </c>
+      <c r="J62" t="s">
+        <v>175</v>
+      </c>
+      <c r="K62" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="63" spans="1:13">
       <c r="A63" s="5" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>336</v>
-      </c>
-      <c r="C63" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="D63" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="E63" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="F63" s="7" t="s">
         <v>329</v>
       </c>
-      <c r="G63" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="H63" s="7" t="s">
-        <v>330</v>
-      </c>
-      <c r="I63" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="J63" s="7" t="s">
-        <v>183</v>
+      <c r="C63" t="s">
+        <v>172</v>
+      </c>
+      <c r="D63" t="s">
+        <v>173</v>
+      </c>
+      <c r="E63" t="s">
+        <v>174</v>
+      </c>
+      <c r="F63" t="s">
+        <v>322</v>
+      </c>
+      <c r="G63" t="s">
+        <v>324</v>
+      </c>
+      <c r="H63" t="s">
+        <v>323</v>
+      </c>
+      <c r="I63" t="s">
+        <v>175</v>
+      </c>
+      <c r="J63" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="64" spans="1:13">
       <c r="A64" s="5" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>337</v>
-      </c>
-      <c r="C64" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="D64" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="E64" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="F64" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="G64" s="7" t="s">
         <v>330</v>
       </c>
-      <c r="H64" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="I64" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="J64" s="7" t="s">
-        <v>331</v>
+      <c r="C64" t="s">
+        <v>172</v>
+      </c>
+      <c r="D64" t="s">
+        <v>173</v>
+      </c>
+      <c r="E64" t="s">
+        <v>174</v>
+      </c>
+      <c r="F64" t="s">
+        <v>322</v>
+      </c>
+      <c r="G64" t="s">
+        <v>323</v>
+      </c>
+      <c r="H64" t="s">
+        <v>175</v>
+      </c>
+      <c r="I64" t="s">
+        <v>176</v>
+      </c>
+      <c r="J64" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="65" spans="1:12">
       <c r="A65" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="B65" s="9" t="s">
-        <v>338</v>
-      </c>
-      <c r="C65" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="D65" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="E65" s="7" t="s">
-        <v>341</v>
-      </c>
-      <c r="F65" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="G65" s="7" t="s">
-        <v>342</v>
-      </c>
-      <c r="H65" s="7" t="s">
-        <v>343</v>
+        <v>85</v>
+      </c>
+      <c r="B65" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="C65" t="s">
+        <v>332</v>
+      </c>
+      <c r="D65" t="s">
+        <v>333</v>
+      </c>
+      <c r="E65" t="s">
+        <v>334</v>
+      </c>
+      <c r="F65" t="s">
+        <v>174</v>
+      </c>
+      <c r="G65" t="s">
+        <v>335</v>
+      </c>
+      <c r="H65" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="66" spans="1:12">
       <c r="A66" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="B66" s="9" t="s">
-        <v>344</v>
-      </c>
-      <c r="C66" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="B66" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="C66" t="s">
+        <v>332</v>
+      </c>
+      <c r="D66" t="s">
+        <v>333</v>
+      </c>
+      <c r="E66" t="s">
+        <v>175</v>
+      </c>
+      <c r="F66" t="s">
+        <v>176</v>
+      </c>
+      <c r="G66" t="s">
+        <v>338</v>
+      </c>
+      <c r="H66" t="s">
         <v>339</v>
       </c>
-      <c r="D66" s="7" t="s">
+      <c r="I66" t="s">
         <v>340</v>
       </c>
-      <c r="E66" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="F66" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="G66" s="7" t="s">
-        <v>345</v>
-      </c>
-      <c r="H66" s="7" t="s">
-        <v>346</v>
-      </c>
-      <c r="I66" s="7" t="s">
-        <v>347</v>
-      </c>
-      <c r="J66" s="7" t="s">
-        <v>348</v>
-      </c>
-      <c r="K66" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="L66" s="7" t="s">
-        <v>207</v>
+      <c r="J66" t="s">
+        <v>341</v>
+      </c>
+      <c r="K66" t="s">
+        <v>201</v>
+      </c>
+      <c r="L66" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="67" spans="1:12">
       <c r="A67" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="B67" s="9" t="s">
-        <v>349</v>
-      </c>
-      <c r="C67" s="7" t="s">
-        <v>350</v>
-      </c>
-      <c r="D67" s="7" t="s">
-        <v>351</v>
-      </c>
-      <c r="E67" s="7" t="s">
-        <v>352</v>
-      </c>
-      <c r="F67" s="7" t="s">
-        <v>353</v>
-      </c>
-      <c r="G67" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="B67" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="C67" t="s">
         <v>343</v>
       </c>
-      <c r="H67" s="7" t="s">
+      <c r="D67" t="s">
+        <v>344</v>
+      </c>
+      <c r="E67" t="s">
+        <v>345</v>
+      </c>
+      <c r="F67" t="s">
         <v>346</v>
+      </c>
+      <c r="G67" t="s">
+        <v>336</v>
+      </c>
+      <c r="H67" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="68" spans="1:12">
       <c r="A68" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="B68" s="9" t="s">
-        <v>354</v>
-      </c>
-      <c r="C68" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="D68" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="E68" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="F68" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="G68" s="7" t="s">
-        <v>345</v>
+        <v>88</v>
+      </c>
+      <c r="B68" s="8" t="s">
+        <v>347</v>
+      </c>
+      <c r="C68" t="s">
+        <v>332</v>
+      </c>
+      <c r="D68" t="s">
+        <v>333</v>
+      </c>
+      <c r="E68" t="s">
+        <v>175</v>
+      </c>
+      <c r="F68" t="s">
+        <v>176</v>
+      </c>
+      <c r="G68" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="69" spans="1:12">
-      <c r="A69" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="B69" s="9" t="s">
-        <v>355</v>
-      </c>
-      <c r="C69" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="D69" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="E69" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="F69" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="G69" s="7" t="s">
-        <v>356</v>
+      <c r="A69" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B69" s="8" t="s">
+        <v>348</v>
+      </c>
+      <c r="C69" t="s">
+        <v>332</v>
+      </c>
+      <c r="D69" t="s">
+        <v>333</v>
+      </c>
+      <c r="E69" t="s">
+        <v>175</v>
+      </c>
+      <c r="F69" t="s">
+        <v>176</v>
+      </c>
+      <c r="G69" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="70" spans="1:12">
       <c r="A70" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="B70" s="9" t="s">
-        <v>357</v>
-      </c>
-      <c r="C70" s="7" t="s">
-        <v>358</v>
-      </c>
-      <c r="D70" s="7" t="s">
-        <v>359</v>
+        <v>90</v>
+      </c>
+      <c r="B70" s="8" t="s">
+        <v>350</v>
+      </c>
+      <c r="C70" t="s">
+        <v>351</v>
+      </c>
+      <c r="D70" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="71" spans="1:12">
       <c r="A71" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="B71" s="9" t="s">
-        <v>360</v>
-      </c>
-      <c r="C71" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="D71" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="E71" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="F71" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="G71" s="7" t="s">
-        <v>361</v>
+        <v>91</v>
+      </c>
+      <c r="B71" s="8" t="s">
+        <v>353</v>
+      </c>
+      <c r="C71" t="s">
+        <v>332</v>
+      </c>
+      <c r="D71" t="s">
+        <v>333</v>
+      </c>
+      <c r="E71" t="s">
+        <v>175</v>
+      </c>
+      <c r="F71" t="s">
+        <v>176</v>
+      </c>
+      <c r="G71" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="72" spans="1:12">
       <c r="A72" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="B72" s="9" t="s">
-        <v>362</v>
-      </c>
-      <c r="C72" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="D72" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="E72" s="7" t="s">
-        <v>343</v>
-      </c>
-      <c r="F72" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="G72" s="7" t="s">
-        <v>183</v>
+        <v>92</v>
+      </c>
+      <c r="B72" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="C72" t="s">
+        <v>332</v>
+      </c>
+      <c r="D72" t="s">
+        <v>333</v>
+      </c>
+      <c r="E72" t="s">
+        <v>336</v>
+      </c>
+      <c r="F72" t="s">
+        <v>175</v>
+      </c>
+      <c r="G72" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="73" spans="1:12">
       <c r="A73" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="B73" s="9" t="s">
-        <v>363</v>
-      </c>
-      <c r="C73" s="7" t="s">
-        <v>342</v>
-      </c>
-      <c r="D73" s="7" t="s">
-        <v>364</v>
-      </c>
-      <c r="E73" s="7" t="s">
-        <v>365</v>
-      </c>
-      <c r="F73" s="7" t="s">
-        <v>366</v>
-      </c>
-      <c r="G73" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="H73" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="I73" s="7" t="s">
-        <v>343</v>
+        <v>93</v>
+      </c>
+      <c r="B73" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="C73" t="s">
+        <v>335</v>
+      </c>
+      <c r="D73" t="s">
+        <v>357</v>
+      </c>
+      <c r="E73" t="s">
+        <v>358</v>
+      </c>
+      <c r="F73" t="s">
+        <v>359</v>
+      </c>
+      <c r="G73" t="s">
+        <v>175</v>
+      </c>
+      <c r="H73" t="s">
+        <v>176</v>
+      </c>
+      <c r="I73" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="74" spans="1:12">
       <c r="A74" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="B74" s="9" t="s">
-        <v>367</v>
-      </c>
-      <c r="C74" s="7" t="s">
-        <v>342</v>
-      </c>
-      <c r="D74" s="7" t="s">
-        <v>368</v>
-      </c>
-      <c r="E74" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="F74" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="G74" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="H74" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="I74" s="7" t="s">
-        <v>343</v>
+        <v>94</v>
+      </c>
+      <c r="B74" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="C74" t="s">
+        <v>335</v>
+      </c>
+      <c r="D74" t="s">
+        <v>361</v>
+      </c>
+      <c r="E74" t="s">
+        <v>332</v>
+      </c>
+      <c r="F74" t="s">
+        <v>333</v>
+      </c>
+      <c r="G74" t="s">
+        <v>175</v>
+      </c>
+      <c r="H74" t="s">
+        <v>176</v>
+      </c>
+      <c r="I74" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="75" spans="1:12">
       <c r="A75" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="B75" s="9" t="s">
-        <v>369</v>
-      </c>
-      <c r="C75" s="7" t="s">
-        <v>342</v>
-      </c>
-      <c r="D75" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="E75" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="F75" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="G75" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="H75" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="I75" s="7" t="s">
-        <v>343</v>
+        <v>95</v>
+      </c>
+      <c r="B75" s="8" t="s">
+        <v>362</v>
+      </c>
+      <c r="C75" t="s">
+        <v>335</v>
+      </c>
+      <c r="D75" t="s">
+        <v>363</v>
+      </c>
+      <c r="E75" t="s">
+        <v>332</v>
+      </c>
+      <c r="F75" t="s">
+        <v>333</v>
+      </c>
+      <c r="G75" t="s">
+        <v>175</v>
+      </c>
+      <c r="H75" t="s">
+        <v>176</v>
+      </c>
+      <c r="I75" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="76" spans="1:12">
       <c r="A76" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="B76" s="9" t="s">
-        <v>371</v>
-      </c>
-      <c r="C76" s="7" t="s">
-        <v>342</v>
-      </c>
-      <c r="D76" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="E76" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="F76" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="G76" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="H76" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="I76" s="7" t="s">
-        <v>343</v>
+        <v>96</v>
+      </c>
+      <c r="B76" s="8" t="s">
+        <v>364</v>
+      </c>
+      <c r="C76" t="s">
+        <v>335</v>
+      </c>
+      <c r="D76" t="s">
+        <v>363</v>
+      </c>
+      <c r="E76" t="s">
+        <v>332</v>
+      </c>
+      <c r="F76" t="s">
+        <v>333</v>
+      </c>
+      <c r="G76" t="s">
+        <v>175</v>
+      </c>
+      <c r="H76" t="s">
+        <v>176</v>
+      </c>
+      <c r="I76" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="77" spans="1:12">
       <c r="A77" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="B77" s="9" t="s">
-        <v>372</v>
-      </c>
-      <c r="C77" s="7" t="s">
-        <v>342</v>
-      </c>
-      <c r="D77" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="E77" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="F77" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="G77" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="H77" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="I77" s="7" t="s">
-        <v>343</v>
+        <v>97</v>
+      </c>
+      <c r="B77" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="C77" t="s">
+        <v>335</v>
+      </c>
+      <c r="D77" t="s">
+        <v>363</v>
+      </c>
+      <c r="E77" t="s">
+        <v>332</v>
+      </c>
+      <c r="F77" t="s">
+        <v>333</v>
+      </c>
+      <c r="G77" t="s">
+        <v>175</v>
+      </c>
+      <c r="H77" t="s">
+        <v>176</v>
+      </c>
+      <c r="I77" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="78" spans="1:12">
       <c r="A78" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="B78" s="9" t="s">
-        <v>373</v>
-      </c>
-      <c r="C78" s="7" t="s">
-        <v>374</v>
-      </c>
-      <c r="D78" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="E78" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="F78" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="G78" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="H78" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="I78" s="7" t="s">
-        <v>343</v>
+        <v>98</v>
+      </c>
+      <c r="B78" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="C78" t="s">
+        <v>367</v>
+      </c>
+      <c r="D78" t="s">
+        <v>363</v>
+      </c>
+      <c r="E78" t="s">
+        <v>332</v>
+      </c>
+      <c r="F78" t="s">
+        <v>333</v>
+      </c>
+      <c r="G78" t="s">
+        <v>175</v>
+      </c>
+      <c r="H78" t="s">
+        <v>176</v>
+      </c>
+      <c r="I78" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="79" spans="1:12">
       <c r="A79" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="B79" s="9" t="s">
-        <v>375</v>
-      </c>
-      <c r="C79" s="7" t="s">
-        <v>374</v>
-      </c>
-      <c r="D79" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="E79" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="F79" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="G79" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="H79" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="I79" s="7" t="s">
-        <v>343</v>
+        <v>99</v>
+      </c>
+      <c r="B79" s="8" t="s">
+        <v>368</v>
+      </c>
+      <c r="C79" t="s">
+        <v>367</v>
+      </c>
+      <c r="D79" t="s">
+        <v>363</v>
+      </c>
+      <c r="E79" t="s">
+        <v>332</v>
+      </c>
+      <c r="F79" t="s">
+        <v>333</v>
+      </c>
+      <c r="G79" t="s">
+        <v>175</v>
+      </c>
+      <c r="H79" t="s">
+        <v>176</v>
+      </c>
+      <c r="I79" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="80" spans="1:12">
       <c r="A80" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="B80" s="9" t="s">
-        <v>376</v>
-      </c>
-      <c r="C80" s="7" t="s">
-        <v>374</v>
-      </c>
-      <c r="D80" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="E80" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="F80" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="G80" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="H80" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="I80" s="7" t="s">
-        <v>343</v>
+        <v>100</v>
+      </c>
+      <c r="B80" s="8" t="s">
+        <v>369</v>
+      </c>
+      <c r="C80" t="s">
+        <v>367</v>
+      </c>
+      <c r="D80" t="s">
+        <v>363</v>
+      </c>
+      <c r="E80" t="s">
+        <v>332</v>
+      </c>
+      <c r="F80" t="s">
+        <v>333</v>
+      </c>
+      <c r="G80" t="s">
+        <v>175</v>
+      </c>
+      <c r="H80" t="s">
+        <v>176</v>
+      </c>
+      <c r="I80" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="81" spans="1:10">
       <c r="A81" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="B81" s="9" t="s">
-        <v>377</v>
-      </c>
-      <c r="C81" s="7" t="s">
-        <v>374</v>
-      </c>
-      <c r="D81" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="B81" s="8" t="s">
         <v>370</v>
       </c>
-      <c r="E81" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="F81" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="G81" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="H81" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="I81" s="7" t="s">
-        <v>343</v>
+      <c r="C81" t="s">
+        <v>367</v>
+      </c>
+      <c r="D81" t="s">
+        <v>363</v>
+      </c>
+      <c r="E81" t="s">
+        <v>332</v>
+      </c>
+      <c r="F81" t="s">
+        <v>333</v>
+      </c>
+      <c r="G81" t="s">
+        <v>175</v>
+      </c>
+      <c r="H81" t="s">
+        <v>176</v>
+      </c>
+      <c r="I81" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="82" spans="1:10">
       <c r="A82" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="B82" s="9" t="s">
-        <v>378</v>
-      </c>
-      <c r="C82" s="7" t="s">
-        <v>374</v>
-      </c>
-      <c r="D82" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="E82" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="F82" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="G82" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="H82" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="I82" s="7" t="s">
-        <v>343</v>
+        <v>102</v>
+      </c>
+      <c r="B82" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="C82" t="s">
+        <v>367</v>
+      </c>
+      <c r="D82" t="s">
+        <v>363</v>
+      </c>
+      <c r="E82" t="s">
+        <v>332</v>
+      </c>
+      <c r="F82" t="s">
+        <v>333</v>
+      </c>
+      <c r="G82" t="s">
+        <v>175</v>
+      </c>
+      <c r="H82" t="s">
+        <v>176</v>
+      </c>
+      <c r="I82" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="83" spans="1:10">
       <c r="A83" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="B83" s="9" t="s">
-        <v>379</v>
-      </c>
-      <c r="C83" s="7" t="s">
-        <v>374</v>
-      </c>
-      <c r="D83" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="E83" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="F83" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="G83" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="H83" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="I83" s="7" t="s">
-        <v>343</v>
+        <v>103</v>
+      </c>
+      <c r="B83" s="8" t="s">
+        <v>372</v>
+      </c>
+      <c r="C83" t="s">
+        <v>367</v>
+      </c>
+      <c r="D83" t="s">
+        <v>363</v>
+      </c>
+      <c r="E83" t="s">
+        <v>332</v>
+      </c>
+      <c r="F83" t="s">
+        <v>333</v>
+      </c>
+      <c r="G83" t="s">
+        <v>175</v>
+      </c>
+      <c r="H83" t="s">
+        <v>176</v>
+      </c>
+      <c r="I83" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="84" spans="1:10">
       <c r="A84" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="B84" s="9" t="s">
-        <v>380</v>
-      </c>
-      <c r="C84" s="7" t="s">
-        <v>374</v>
-      </c>
-      <c r="D84" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="E84" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="F84" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="G84" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="H84" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="I84" s="7" t="s">
-        <v>343</v>
+        <v>104</v>
+      </c>
+      <c r="B84" s="8" t="s">
+        <v>373</v>
+      </c>
+      <c r="C84" t="s">
+        <v>367</v>
+      </c>
+      <c r="D84" t="s">
+        <v>363</v>
+      </c>
+      <c r="E84" t="s">
+        <v>332</v>
+      </c>
+      <c r="F84" t="s">
+        <v>333</v>
+      </c>
+      <c r="G84" t="s">
+        <v>175</v>
+      </c>
+      <c r="H84" t="s">
+        <v>176</v>
+      </c>
+      <c r="I84" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="85" spans="1:10">
       <c r="A85" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="B85" s="9" t="s">
-        <v>381</v>
-      </c>
-      <c r="C85" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="B85" s="8" t="s">
         <v>374</v>
       </c>
-      <c r="D85" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="E85" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="F85" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="G85" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="H85" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="I85" s="7" t="s">
-        <v>343</v>
+      <c r="C85" t="s">
+        <v>367</v>
+      </c>
+      <c r="D85" t="s">
+        <v>363</v>
+      </c>
+      <c r="E85" t="s">
+        <v>332</v>
+      </c>
+      <c r="F85" t="s">
+        <v>333</v>
+      </c>
+      <c r="G85" t="s">
+        <v>175</v>
+      </c>
+      <c r="H85" t="s">
+        <v>176</v>
+      </c>
+      <c r="I85" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="86" spans="1:10">
       <c r="A86" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="B86" s="9" t="s">
-        <v>382</v>
-      </c>
-      <c r="C86" s="7" t="s">
-        <v>374</v>
-      </c>
-      <c r="D86" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="E86" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="F86" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="G86" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="H86" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="I86" s="7" t="s">
-        <v>343</v>
+        <v>106</v>
+      </c>
+      <c r="B86" s="8" t="s">
+        <v>375</v>
+      </c>
+      <c r="C86" t="s">
+        <v>367</v>
+      </c>
+      <c r="D86" t="s">
+        <v>363</v>
+      </c>
+      <c r="E86" t="s">
+        <v>332</v>
+      </c>
+      <c r="F86" t="s">
+        <v>333</v>
+      </c>
+      <c r="G86" t="s">
+        <v>175</v>
+      </c>
+      <c r="H86" t="s">
+        <v>176</v>
+      </c>
+      <c r="I86" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="87" spans="1:10">
       <c r="A87" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="B87" s="9" t="s">
-        <v>383</v>
-      </c>
-      <c r="C87" s="7" t="s">
-        <v>374</v>
-      </c>
-      <c r="D87" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="E87" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="F87" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="G87" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="H87" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="I87" s="7" t="s">
-        <v>343</v>
+        <v>107</v>
+      </c>
+      <c r="B87" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="C87" t="s">
+        <v>367</v>
+      </c>
+      <c r="D87" t="s">
+        <v>363</v>
+      </c>
+      <c r="E87" t="s">
+        <v>332</v>
+      </c>
+      <c r="F87" t="s">
+        <v>333</v>
+      </c>
+      <c r="G87" t="s">
+        <v>175</v>
+      </c>
+      <c r="H87" t="s">
+        <v>176</v>
+      </c>
+      <c r="I87" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="88" spans="1:10">
-      <c r="A88" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="B88" s="9" t="s">
-        <v>384</v>
-      </c>
-      <c r="C88" s="7" t="s">
-        <v>374</v>
-      </c>
-      <c r="D88" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="E88" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="F88" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="G88" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="H88" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="I88" s="7" t="s">
-        <v>343</v>
+      <c r="A88" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="B88" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="C88" t="s">
+        <v>367</v>
+      </c>
+      <c r="D88" t="s">
+        <v>363</v>
+      </c>
+      <c r="E88" t="s">
+        <v>332</v>
+      </c>
+      <c r="F88" t="s">
+        <v>333</v>
+      </c>
+      <c r="G88" t="s">
+        <v>175</v>
+      </c>
+      <c r="H88" t="s">
+        <v>176</v>
+      </c>
+      <c r="I88" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="89" spans="1:10">
       <c r="A89" s="5" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="B89" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="C89" t="s">
+        <v>379</v>
+      </c>
+      <c r="D89" t="s">
+        <v>380</v>
+      </c>
+      <c r="E89" t="s">
+        <v>381</v>
+      </c>
+      <c r="F89" t="s">
+        <v>382</v>
+      </c>
+      <c r="G89" t="s">
+        <v>383</v>
+      </c>
+      <c r="H89" t="s">
+        <v>384</v>
+      </c>
+      <c r="I89" t="s">
         <v>385</v>
-      </c>
-      <c r="C89" s="7" t="s">
-        <v>386</v>
-      </c>
-      <c r="D89" s="7" t="s">
-        <v>387</v>
-      </c>
-      <c r="E89" s="7" t="s">
-        <v>388</v>
-      </c>
-      <c r="F89" s="7" t="s">
-        <v>389</v>
-      </c>
-      <c r="G89" s="7" t="s">
-        <v>390</v>
-      </c>
-      <c r="H89" s="7" t="s">
-        <v>391</v>
-      </c>
-      <c r="I89" s="7" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="90" spans="1:10">
       <c r="A90" s="5" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>393</v>
-      </c>
-      <c r="C90" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="D90" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="E90" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="F90" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="G90" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="H90" s="7" t="s">
-        <v>394</v>
-      </c>
-      <c r="I90" s="7" t="s">
-        <v>395</v>
-      </c>
-      <c r="J90" s="7" t="s">
-        <v>396</v>
+        <v>386</v>
+      </c>
+      <c r="C90" t="s">
+        <v>172</v>
+      </c>
+      <c r="D90" t="s">
+        <v>173</v>
+      </c>
+      <c r="E90" t="s">
+        <v>174</v>
+      </c>
+      <c r="F90" t="s">
+        <v>175</v>
+      </c>
+      <c r="G90" t="s">
+        <v>176</v>
+      </c>
+      <c r="H90" t="s">
+        <v>387</v>
+      </c>
+      <c r="I90" t="s">
+        <v>388</v>
+      </c>
+      <c r="J90" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="91" spans="1:10">
       <c r="A91" s="5" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>397</v>
-      </c>
-      <c r="C91" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="D91" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="E91" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="F91" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="G91" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="H91" s="7" t="s">
-        <v>395</v>
-      </c>
-      <c r="I91" s="7" t="s">
-        <v>398</v>
+        <v>390</v>
+      </c>
+      <c r="C91" t="s">
+        <v>172</v>
+      </c>
+      <c r="D91" t="s">
+        <v>173</v>
+      </c>
+      <c r="E91" t="s">
+        <v>174</v>
+      </c>
+      <c r="F91" t="s">
+        <v>175</v>
+      </c>
+      <c r="G91" t="s">
+        <v>176</v>
+      </c>
+      <c r="H91" t="s">
+        <v>388</v>
+      </c>
+      <c r="I91" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="92" spans="1:10">
       <c r="A92" s="5" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>399</v>
-      </c>
-      <c r="C92" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="D92" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="E92" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="F92" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="G92" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="H92" s="7" t="s">
-        <v>400</v>
-      </c>
-      <c r="I92" s="7" t="s">
-        <v>343</v>
+        <v>392</v>
+      </c>
+      <c r="C92" t="s">
+        <v>172</v>
+      </c>
+      <c r="D92" t="s">
+        <v>173</v>
+      </c>
+      <c r="E92" t="s">
+        <v>174</v>
+      </c>
+      <c r="F92" t="s">
+        <v>175</v>
+      </c>
+      <c r="G92" t="s">
+        <v>176</v>
+      </c>
+      <c r="H92" t="s">
+        <v>393</v>
+      </c>
+      <c r="I92" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="93" spans="1:10">
       <c r="A93" s="5" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>401</v>
-      </c>
-      <c r="C93" s="7" t="s">
-        <v>342</v>
-      </c>
-      <c r="D93" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="E93" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="F93" s="7" t="s">
-        <v>365</v>
-      </c>
-      <c r="G93" s="7" t="s">
-        <v>366</v>
-      </c>
-      <c r="H93" s="7" t="s">
-        <v>389</v>
-      </c>
-      <c r="I93" s="7" t="s">
-        <v>402</v>
+        <v>394</v>
+      </c>
+      <c r="C93" t="s">
+        <v>335</v>
+      </c>
+      <c r="D93" t="s">
+        <v>175</v>
+      </c>
+      <c r="E93" t="s">
+        <v>176</v>
+      </c>
+      <c r="F93" t="s">
+        <v>358</v>
+      </c>
+      <c r="G93" t="s">
+        <v>359</v>
+      </c>
+      <c r="H93" t="s">
+        <v>382</v>
+      </c>
+      <c r="I93" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="94" spans="1:10">
-      <c r="A94" s="8" t="s">
-        <v>123</v>
+      <c r="A94" s="7" t="s">
+        <v>116</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>403</v>
-      </c>
-      <c r="C94" s="7" t="s">
-        <v>404</v>
-      </c>
-      <c r="D94" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="E94" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="F94" s="7" t="s">
-        <v>405</v>
-      </c>
-      <c r="G94" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="H94" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="I94" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="J94" s="7" t="s">
-        <v>406</v>
+        <v>396</v>
+      </c>
+      <c r="C94" t="s">
+        <v>397</v>
+      </c>
+      <c r="D94" t="s">
+        <v>172</v>
+      </c>
+      <c r="E94" t="s">
+        <v>173</v>
+      </c>
+      <c r="F94" t="s">
+        <v>398</v>
+      </c>
+      <c r="G94" t="s">
+        <v>174</v>
+      </c>
+      <c r="H94" t="s">
+        <v>175</v>
+      </c>
+      <c r="I94" t="s">
+        <v>176</v>
+      </c>
+      <c r="J94" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="95" spans="1:10">
       <c r="A95" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="B95" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="B95" s="8" t="s">
+        <v>400</v>
+      </c>
+      <c r="C95" t="s">
+        <v>401</v>
+      </c>
+      <c r="D95" t="s">
+        <v>402</v>
+      </c>
+      <c r="E95" t="s">
+        <v>403</v>
+      </c>
+      <c r="F95" t="s">
+        <v>404</v>
+      </c>
+      <c r="G95" t="s">
+        <v>405</v>
+      </c>
+      <c r="H95" t="s">
+        <v>406</v>
+      </c>
+      <c r="I95" t="s">
         <v>407</v>
-      </c>
-      <c r="C95" s="7" t="s">
-        <v>408</v>
-      </c>
-      <c r="D95" s="7" t="s">
-        <v>409</v>
-      </c>
-      <c r="E95" s="7" t="s">
-        <v>410</v>
-      </c>
-      <c r="F95" s="7" t="s">
-        <v>411</v>
-      </c>
-      <c r="G95" s="7" t="s">
-        <v>412</v>
-      </c>
-      <c r="H95" s="7" t="s">
-        <v>413</v>
-      </c>
-      <c r="I95" s="7" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="96" spans="1:10">
       <c r="A96" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="B96" s="9" t="s">
-        <v>415</v>
-      </c>
-      <c r="C96" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="D96" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="E96" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="B96" s="8" t="s">
+        <v>408</v>
+      </c>
+      <c r="C96" t="s">
+        <v>172</v>
+      </c>
+      <c r="D96" t="s">
+        <v>173</v>
+      </c>
+      <c r="E96" t="s">
+        <v>405</v>
+      </c>
+      <c r="F96" t="s">
+        <v>404</v>
+      </c>
+      <c r="G96" t="s">
+        <v>409</v>
+      </c>
+      <c r="H96" t="s">
+        <v>410</v>
+      </c>
+      <c r="I96" t="s">
+        <v>411</v>
+      </c>
+      <c r="J96" t="s">
         <v>412</v>
-      </c>
-      <c r="F96" s="7" t="s">
-        <v>411</v>
-      </c>
-      <c r="G96" s="7" t="s">
-        <v>416</v>
-      </c>
-      <c r="H96" s="7" t="s">
-        <v>417</v>
-      </c>
-      <c r="I96" s="7" t="s">
-        <v>418</v>
-      </c>
-      <c r="J96" s="7" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="97" spans="1:11">
       <c r="A97" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="B97" s="9" t="s">
-        <v>420</v>
-      </c>
-      <c r="C97" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="D97" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="E97" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="B97" s="8" t="s">
+        <v>413</v>
+      </c>
+      <c r="C97" t="s">
+        <v>172</v>
+      </c>
+      <c r="D97" t="s">
+        <v>173</v>
+      </c>
+      <c r="E97" t="s">
+        <v>405</v>
+      </c>
+      <c r="F97" t="s">
+        <v>404</v>
+      </c>
+      <c r="G97" t="s">
+        <v>409</v>
+      </c>
+      <c r="H97" t="s">
+        <v>410</v>
+      </c>
+      <c r="I97" t="s">
+        <v>411</v>
+      </c>
+      <c r="J97" t="s">
         <v>412</v>
-      </c>
-      <c r="F97" s="7" t="s">
-        <v>411</v>
-      </c>
-      <c r="G97" s="7" t="s">
-        <v>416</v>
-      </c>
-      <c r="H97" s="7" t="s">
-        <v>417</v>
-      </c>
-      <c r="I97" s="7" t="s">
-        <v>418</v>
-      </c>
-      <c r="J97" s="7" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="98" spans="1:11">
       <c r="A98" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B98" s="9" t="s">
-        <v>421</v>
-      </c>
-      <c r="C98" s="7" t="s">
-        <v>422</v>
-      </c>
-      <c r="D98" s="7" t="s">
-        <v>423</v>
-      </c>
-      <c r="E98" s="7" t="s">
-        <v>412</v>
-      </c>
-      <c r="F98" s="7" t="s">
-        <v>411</v>
-      </c>
-      <c r="G98" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="H98" s="7" t="s">
-        <v>424</v>
-      </c>
-      <c r="I98" s="7" t="s">
-        <v>425</v>
+        <v>122</v>
+      </c>
+      <c r="B98" s="8" t="s">
+        <v>414</v>
+      </c>
+      <c r="C98" t="s">
+        <v>415</v>
+      </c>
+      <c r="D98" t="s">
+        <v>416</v>
+      </c>
+      <c r="E98" t="s">
+        <v>405</v>
+      </c>
+      <c r="F98" t="s">
+        <v>404</v>
+      </c>
+      <c r="G98" t="s">
+        <v>217</v>
+      </c>
+      <c r="H98" t="s">
+        <v>417</v>
+      </c>
+      <c r="I98" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="99" spans="1:11">
       <c r="A99" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="B99" s="9" t="s">
-        <v>426</v>
-      </c>
-      <c r="C99" s="7" t="s">
-        <v>422</v>
-      </c>
-      <c r="D99" s="7" t="s">
-        <v>423</v>
-      </c>
-      <c r="E99" s="7" t="s">
-        <v>412</v>
-      </c>
-      <c r="F99" s="7" t="s">
-        <v>411</v>
-      </c>
-      <c r="G99" s="7" t="s">
-        <v>427</v>
-      </c>
-      <c r="H99" s="7" t="s">
-        <v>428</v>
-      </c>
-      <c r="I99" s="7" t="s">
-        <v>424</v>
+        <v>123</v>
+      </c>
+      <c r="B99" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="C99" t="s">
+        <v>415</v>
+      </c>
+      <c r="D99" t="s">
+        <v>416</v>
+      </c>
+      <c r="E99" t="s">
+        <v>405</v>
+      </c>
+      <c r="F99" t="s">
+        <v>404</v>
+      </c>
+      <c r="G99" t="s">
+        <v>420</v>
+      </c>
+      <c r="H99" t="s">
+        <v>421</v>
+      </c>
+      <c r="I99" t="s">
+        <v>417</v>
       </c>
     </row>
     <row r="100" spans="1:11">
       <c r="A100" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="B100" s="9" t="s">
-        <v>429</v>
-      </c>
-      <c r="C100" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="D100" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="E100" s="7" t="s">
-        <v>412</v>
-      </c>
-      <c r="F100" s="7" t="s">
-        <v>411</v>
-      </c>
-      <c r="G100" s="7" t="s">
-        <v>430</v>
-      </c>
-      <c r="H100" s="7" t="s">
-        <v>431</v>
-      </c>
-      <c r="I100" s="7" t="s">
-        <v>432</v>
+        <v>124</v>
+      </c>
+      <c r="B100" s="8" t="s">
+        <v>422</v>
+      </c>
+      <c r="C100" t="s">
+        <v>203</v>
+      </c>
+      <c r="D100" t="s">
+        <v>204</v>
+      </c>
+      <c r="E100" t="s">
+        <v>405</v>
+      </c>
+      <c r="F100" t="s">
+        <v>404</v>
+      </c>
+      <c r="G100" t="s">
+        <v>423</v>
+      </c>
+      <c r="H100" t="s">
+        <v>424</v>
+      </c>
+      <c r="I100" t="s">
+        <v>425</v>
       </c>
     </row>
     <row r="101" spans="1:11">
       <c r="A101" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="B101" s="9" t="s">
-        <v>433</v>
-      </c>
-      <c r="C101" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="D101" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="E101" s="7" t="s">
-        <v>412</v>
-      </c>
-      <c r="F101" s="7" t="s">
-        <v>411</v>
-      </c>
-      <c r="G101" s="7" t="s">
-        <v>431</v>
-      </c>
-      <c r="H101" s="7" t="s">
-        <v>396</v>
-      </c>
-      <c r="I101" s="7" t="s">
-        <v>432</v>
+        <v>125</v>
+      </c>
+      <c r="B101" s="8" t="s">
+        <v>426</v>
+      </c>
+      <c r="C101" t="s">
+        <v>203</v>
+      </c>
+      <c r="D101" t="s">
+        <v>204</v>
+      </c>
+      <c r="E101" t="s">
+        <v>405</v>
+      </c>
+      <c r="F101" t="s">
+        <v>404</v>
+      </c>
+      <c r="G101" t="s">
+        <v>424</v>
+      </c>
+      <c r="H101" t="s">
+        <v>389</v>
+      </c>
+      <c r="I101" t="s">
+        <v>425</v>
       </c>
     </row>
     <row r="102" spans="1:11">
       <c r="A102" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="B102" s="9" t="s">
-        <v>434</v>
-      </c>
-      <c r="C102" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="D102" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="E102" s="7" t="s">
-        <v>412</v>
-      </c>
-      <c r="F102" s="7" t="s">
-        <v>411</v>
-      </c>
-      <c r="G102" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="B102" s="8" t="s">
         <v>427</v>
       </c>
-      <c r="H102" s="7" t="s">
-        <v>435</v>
-      </c>
-      <c r="I102" s="7" t="s">
-        <v>413</v>
+      <c r="C102" t="s">
+        <v>203</v>
+      </c>
+      <c r="D102" t="s">
+        <v>204</v>
+      </c>
+      <c r="E102" t="s">
+        <v>405</v>
+      </c>
+      <c r="F102" t="s">
+        <v>404</v>
+      </c>
+      <c r="G102" t="s">
+        <v>420</v>
+      </c>
+      <c r="H102" t="s">
+        <v>428</v>
+      </c>
+      <c r="I102" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="103" spans="1:11">
       <c r="A103" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="B103" s="9" t="s">
-        <v>436</v>
-      </c>
-      <c r="C103" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="D103" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="E103" s="7" t="s">
-        <v>412</v>
-      </c>
-      <c r="F103" s="7" t="s">
-        <v>411</v>
-      </c>
-      <c r="G103" s="7" t="s">
-        <v>427</v>
-      </c>
-      <c r="H103" s="7" t="s">
-        <v>437</v>
-      </c>
-      <c r="I103" s="7" t="s">
-        <v>438</v>
-      </c>
-      <c r="J103" s="7" t="s">
-        <v>439</v>
-      </c>
-      <c r="K103" s="7" t="s">
-        <v>440</v>
+        <v>127</v>
+      </c>
+      <c r="B103" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="C103" t="s">
+        <v>203</v>
+      </c>
+      <c r="D103" t="s">
+        <v>204</v>
+      </c>
+      <c r="E103" t="s">
+        <v>405</v>
+      </c>
+      <c r="F103" t="s">
+        <v>404</v>
+      </c>
+      <c r="G103" t="s">
+        <v>420</v>
+      </c>
+      <c r="H103" t="s">
+        <v>430</v>
+      </c>
+      <c r="I103" t="s">
+        <v>431</v>
+      </c>
+      <c r="J103" t="s">
+        <v>432</v>
+      </c>
+      <c r="K103" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="104" spans="1:11">
       <c r="A104" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="B104" s="9" t="s">
-        <v>441</v>
-      </c>
-      <c r="C104" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="D104" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="E104" s="7" t="s">
-        <v>412</v>
-      </c>
-      <c r="F104" s="7" t="s">
-        <v>411</v>
-      </c>
-      <c r="G104" s="7" t="s">
-        <v>442</v>
-      </c>
-      <c r="H104" s="7" t="s">
-        <v>343</v>
-      </c>
-      <c r="I104" s="7" t="s">
-        <v>443</v>
+        <v>128</v>
+      </c>
+      <c r="B104" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="C104" t="s">
+        <v>203</v>
+      </c>
+      <c r="D104" t="s">
+        <v>204</v>
+      </c>
+      <c r="E104" t="s">
+        <v>405</v>
+      </c>
+      <c r="F104" t="s">
+        <v>404</v>
+      </c>
+      <c r="G104" t="s">
+        <v>435</v>
+      </c>
+      <c r="H104" t="s">
+        <v>336</v>
+      </c>
+      <c r="I104" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="105" spans="1:11">
       <c r="A105" s="5" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="B105" s="6" t="s">
+        <v>437</v>
+      </c>
+      <c r="C105" t="s">
+        <v>203</v>
+      </c>
+      <c r="D105" t="s">
+        <v>204</v>
+      </c>
+      <c r="E105" t="s">
+        <v>438</v>
+      </c>
+      <c r="F105" t="s">
+        <v>439</v>
+      </c>
+      <c r="G105" t="s">
+        <v>440</v>
+      </c>
+      <c r="H105" t="s">
+        <v>441</v>
+      </c>
+      <c r="I105" t="s">
+        <v>442</v>
+      </c>
+      <c r="J105" t="s">
+        <v>443</v>
+      </c>
+      <c r="K105" t="s">
         <v>444</v>
-      </c>
-      <c r="C105" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="D105" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="E105" s="7" t="s">
-        <v>445</v>
-      </c>
-      <c r="F105" s="7" t="s">
-        <v>446</v>
-      </c>
-      <c r="G105" s="7" t="s">
-        <v>447</v>
-      </c>
-      <c r="H105" s="7" t="s">
-        <v>448</v>
-      </c>
-      <c r="I105" s="7" t="s">
-        <v>449</v>
-      </c>
-      <c r="J105" s="7" t="s">
-        <v>450</v>
-      </c>
-      <c r="K105" s="7" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="106" spans="1:11">
       <c r="A106" s="5" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>452</v>
-      </c>
-      <c r="C106" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="D106" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="E106" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="F106" s="7" t="s">
-        <v>453</v>
-      </c>
-      <c r="G106" s="7" t="s">
-        <v>447</v>
-      </c>
-      <c r="H106" s="7" t="s">
-        <v>448</v>
-      </c>
-      <c r="I106" s="7" t="s">
-        <v>451</v>
+        <v>445</v>
+      </c>
+      <c r="C106" t="s">
+        <v>203</v>
+      </c>
+      <c r="D106" t="s">
+        <v>205</v>
+      </c>
+      <c r="E106" t="s">
+        <v>204</v>
+      </c>
+      <c r="F106" t="s">
+        <v>446</v>
+      </c>
+      <c r="G106" t="s">
+        <v>440</v>
+      </c>
+      <c r="H106" t="s">
+        <v>441</v>
+      </c>
+      <c r="I106" t="s">
+        <v>444</v>
       </c>
     </row>
     <row r="107" spans="1:11">
       <c r="A107" s="5" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>454</v>
-      </c>
-      <c r="C107" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="D107" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="E107" s="7" t="s">
-        <v>453</v>
-      </c>
-      <c r="F107" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="G107" s="7" t="s">
         <v>447</v>
       </c>
-      <c r="H107" s="7" t="s">
-        <v>448</v>
-      </c>
-      <c r="I107" s="7" t="s">
-        <v>451</v>
+      <c r="C107" t="s">
+        <v>203</v>
+      </c>
+      <c r="D107" t="s">
+        <v>204</v>
+      </c>
+      <c r="E107" t="s">
+        <v>446</v>
+      </c>
+      <c r="F107" t="s">
+        <v>205</v>
+      </c>
+      <c r="G107" t="s">
+        <v>440</v>
+      </c>
+      <c r="H107" t="s">
+        <v>441</v>
+      </c>
+      <c r="I107" t="s">
+        <v>444</v>
       </c>
     </row>
     <row r="108" spans="1:11">
       <c r="A108" s="5" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>455</v>
-      </c>
-      <c r="C108" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="D108" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="E108" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="F108" s="7" t="s">
-        <v>453</v>
-      </c>
-      <c r="G108" s="7" t="s">
-        <v>447</v>
-      </c>
-      <c r="H108" s="7" t="s">
         <v>448</v>
       </c>
-      <c r="I108" s="7" t="s">
-        <v>451</v>
+      <c r="C108" t="s">
+        <v>203</v>
+      </c>
+      <c r="D108" t="s">
+        <v>204</v>
+      </c>
+      <c r="E108" t="s">
+        <v>205</v>
+      </c>
+      <c r="F108" t="s">
+        <v>446</v>
+      </c>
+      <c r="G108" t="s">
+        <v>440</v>
+      </c>
+      <c r="H108" t="s">
+        <v>441</v>
+      </c>
+      <c r="I108" t="s">
+        <v>444</v>
       </c>
     </row>
     <row r="109" spans="1:11">
       <c r="A109" s="5" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>456</v>
-      </c>
-      <c r="C109" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="D109" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="E109" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="F109" s="7" t="s">
-        <v>453</v>
-      </c>
-      <c r="G109" s="7" t="s">
-        <v>447</v>
-      </c>
-      <c r="H109" s="7" t="s">
-        <v>448</v>
-      </c>
-      <c r="I109" s="7" t="s">
-        <v>451</v>
+        <v>449</v>
+      </c>
+      <c r="C109" t="s">
+        <v>203</v>
+      </c>
+      <c r="D109" t="s">
+        <v>204</v>
+      </c>
+      <c r="E109" t="s">
+        <v>205</v>
+      </c>
+      <c r="F109" t="s">
+        <v>446</v>
+      </c>
+      <c r="G109" t="s">
+        <v>440</v>
+      </c>
+      <c r="H109" t="s">
+        <v>441</v>
+      </c>
+      <c r="I109" t="s">
+        <v>444</v>
       </c>
     </row>
     <row r="110" spans="1:11">
       <c r="A110" s="5" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>457</v>
-      </c>
-      <c r="C110" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="D110" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="E110" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="F110" s="7" t="s">
-        <v>453</v>
-      </c>
-      <c r="G110" s="7" t="s">
-        <v>447</v>
-      </c>
-      <c r="H110" s="7" t="s">
-        <v>448</v>
-      </c>
-      <c r="I110" s="7" t="s">
-        <v>451</v>
+        <v>450</v>
+      </c>
+      <c r="C110" t="s">
+        <v>203</v>
+      </c>
+      <c r="D110" t="s">
+        <v>204</v>
+      </c>
+      <c r="E110" t="s">
+        <v>205</v>
+      </c>
+      <c r="F110" t="s">
+        <v>446</v>
+      </c>
+      <c r="G110" t="s">
+        <v>440</v>
+      </c>
+      <c r="H110" t="s">
+        <v>441</v>
+      </c>
+      <c r="I110" t="s">
+        <v>444</v>
       </c>
     </row>
     <row r="111" spans="1:11">
       <c r="A111" s="5" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>458</v>
-      </c>
-      <c r="C111" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="D111" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="E111" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="F111" s="7" t="s">
-        <v>453</v>
-      </c>
-      <c r="G111" s="7" t="s">
-        <v>447</v>
-      </c>
-      <c r="H111" s="7" t="s">
-        <v>448</v>
-      </c>
-      <c r="I111" s="7" t="s">
         <v>451</v>
+      </c>
+      <c r="C111" t="s">
+        <v>203</v>
+      </c>
+      <c r="D111" t="s">
+        <v>204</v>
+      </c>
+      <c r="E111" t="s">
+        <v>205</v>
+      </c>
+      <c r="F111" t="s">
+        <v>446</v>
+      </c>
+      <c r="G111" t="s">
+        <v>440</v>
+      </c>
+      <c r="H111" t="s">
+        <v>441</v>
+      </c>
+      <c r="I111" t="s">
+        <v>444</v>
       </c>
     </row>
     <row r="112" spans="1:11">
       <c r="A112" s="5" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>459</v>
-      </c>
-      <c r="C112" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="D112" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="E112" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="F112" s="7" t="s">
-        <v>453</v>
-      </c>
-      <c r="G112" s="7" t="s">
-        <v>447</v>
-      </c>
-      <c r="H112" s="7" t="s">
-        <v>448</v>
-      </c>
-      <c r="I112" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
+      </c>
+      <c r="C112" t="s">
+        <v>203</v>
+      </c>
+      <c r="D112" t="s">
+        <v>204</v>
+      </c>
+      <c r="E112" t="s">
+        <v>205</v>
+      </c>
+      <c r="F112" t="s">
+        <v>446</v>
+      </c>
+      <c r="G112" t="s">
+        <v>440</v>
+      </c>
+      <c r="H112" t="s">
+        <v>441</v>
+      </c>
+      <c r="I112" t="s">
+        <v>444</v>
       </c>
     </row>
     <row r="113" spans="1:19">
       <c r="A113" s="5" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>460</v>
-      </c>
-      <c r="C113" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="D113" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="E113" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="F113" s="7" t="s">
         <v>453</v>
       </c>
-      <c r="G113" s="7" t="s">
-        <v>447</v>
-      </c>
-      <c r="H113" s="7" t="s">
-        <v>448</v>
-      </c>
-      <c r="I113" s="7" t="s">
-        <v>451</v>
+      <c r="C113" t="s">
+        <v>203</v>
+      </c>
+      <c r="D113" t="s">
+        <v>204</v>
+      </c>
+      <c r="E113" t="s">
+        <v>205</v>
+      </c>
+      <c r="F113" t="s">
+        <v>446</v>
+      </c>
+      <c r="G113" t="s">
+        <v>440</v>
+      </c>
+      <c r="H113" t="s">
+        <v>441</v>
+      </c>
+      <c r="I113" t="s">
+        <v>444</v>
       </c>
     </row>
     <row r="114" spans="1:19">
       <c r="A114" s="5" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>461</v>
-      </c>
-      <c r="C114" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="D114" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="E114" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="F114" s="7" t="s">
-        <v>453</v>
-      </c>
-      <c r="G114" s="7" t="s">
-        <v>447</v>
-      </c>
-      <c r="H114" s="7" t="s">
-        <v>448</v>
-      </c>
-      <c r="I114" s="7" t="s">
-        <v>451</v>
+        <v>454</v>
+      </c>
+      <c r="C114" t="s">
+        <v>203</v>
+      </c>
+      <c r="D114" t="s">
+        <v>204</v>
+      </c>
+      <c r="E114" t="s">
+        <v>205</v>
+      </c>
+      <c r="F114" t="s">
+        <v>446</v>
+      </c>
+      <c r="G114" t="s">
+        <v>440</v>
+      </c>
+      <c r="H114" t="s">
+        <v>441</v>
+      </c>
+      <c r="I114" t="s">
+        <v>444</v>
       </c>
     </row>
     <row r="115" spans="1:19">
       <c r="A115" s="5" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="B115" s="6" t="s">
+        <v>455</v>
+      </c>
+      <c r="C115" t="s">
+        <v>456</v>
+      </c>
+      <c r="D115" t="s">
+        <v>457</v>
+      </c>
+      <c r="E115" t="s">
+        <v>458</v>
+      </c>
+      <c r="F115" t="s">
+        <v>459</v>
+      </c>
+      <c r="G115" t="s">
+        <v>174</v>
+      </c>
+      <c r="H115" t="s">
+        <v>460</v>
+      </c>
+      <c r="I115" t="s">
+        <v>461</v>
+      </c>
+      <c r="J115" t="s">
         <v>462</v>
       </c>
-      <c r="C115" s="7" t="s">
+      <c r="K115" t="s">
         <v>463</v>
       </c>
-      <c r="D115" s="7" t="s">
+      <c r="L115" t="s">
         <v>464</v>
       </c>
-      <c r="E115" s="7" t="s">
+      <c r="M115" t="s">
         <v>465</v>
       </c>
-      <c r="F115" s="7" t="s">
+      <c r="N115" t="s">
         <v>466</v>
       </c>
-      <c r="G115" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="H115" s="7" t="s">
+      <c r="O115" t="s">
         <v>467</v>
-      </c>
-      <c r="I115" s="7" t="s">
-        <v>468</v>
-      </c>
-      <c r="J115" s="7" t="s">
-        <v>469</v>
-      </c>
-      <c r="K115" s="7" t="s">
-        <v>470</v>
-      </c>
-      <c r="L115" s="7" t="s">
-        <v>471</v>
-      </c>
-      <c r="M115" s="7" t="s">
-        <v>472</v>
-      </c>
-      <c r="N115" s="7" t="s">
-        <v>473</v>
-      </c>
-      <c r="O115" s="7" t="s">
-        <v>474</v>
       </c>
     </row>
     <row r="116" spans="1:19">
       <c r="A116" s="5" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>475</v>
-      </c>
-      <c r="C116" s="7" t="s">
+        <v>468</v>
+      </c>
+      <c r="C116" t="s">
+        <v>456</v>
+      </c>
+      <c r="D116" t="s">
+        <v>469</v>
+      </c>
+      <c r="E116" t="s">
+        <v>458</v>
+      </c>
+      <c r="F116" t="s">
+        <v>460</v>
+      </c>
+      <c r="G116" t="s">
+        <v>470</v>
+      </c>
+      <c r="H116" t="s">
+        <v>471</v>
+      </c>
+      <c r="I116" t="s">
+        <v>464</v>
+      </c>
+      <c r="J116" t="s">
+        <v>465</v>
+      </c>
+      <c r="K116" t="s">
         <v>463</v>
       </c>
-      <c r="D116" s="7" t="s">
-        <v>476</v>
-      </c>
-      <c r="E116" s="7" t="s">
-        <v>465</v>
-      </c>
-      <c r="F116" s="7" t="s">
+      <c r="L116" t="s">
+        <v>466</v>
+      </c>
+      <c r="M116" t="s">
         <v>467</v>
-      </c>
-      <c r="G116" s="7" t="s">
-        <v>477</v>
-      </c>
-      <c r="H116" s="7" t="s">
-        <v>478</v>
-      </c>
-      <c r="I116" s="7" t="s">
-        <v>471</v>
-      </c>
-      <c r="J116" s="7" t="s">
-        <v>472</v>
-      </c>
-      <c r="K116" s="7" t="s">
-        <v>470</v>
-      </c>
-      <c r="L116" s="7" t="s">
-        <v>473</v>
-      </c>
-      <c r="M116" s="7" t="s">
-        <v>474</v>
       </c>
     </row>
     <row r="117" spans="1:19">
       <c r="A117" s="5" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>479</v>
-      </c>
-      <c r="C117" s="7" t="s">
-        <v>480</v>
-      </c>
-      <c r="D117" s="7" t="s">
-        <v>469</v>
-      </c>
-      <c r="E117" s="7" t="s">
-        <v>468</v>
-      </c>
-      <c r="F117" s="7" t="s">
-        <v>466</v>
-      </c>
-      <c r="G117" s="7" t="s">
-        <v>481</v>
-      </c>
-      <c r="H117" s="7" t="s">
-        <v>471</v>
-      </c>
-      <c r="I117" s="7" t="s">
         <v>472</v>
+      </c>
+      <c r="C117" t="s">
+        <v>473</v>
+      </c>
+      <c r="D117" t="s">
+        <v>462</v>
+      </c>
+      <c r="E117" t="s">
+        <v>461</v>
+      </c>
+      <c r="F117" t="s">
+        <v>459</v>
+      </c>
+      <c r="G117" t="s">
+        <v>474</v>
+      </c>
+      <c r="H117" t="s">
+        <v>464</v>
+      </c>
+      <c r="I117" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="118" spans="1:19">
       <c r="A118" s="5" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>482</v>
-      </c>
-      <c r="C118" s="7" t="s">
-        <v>483</v>
-      </c>
-      <c r="D118" s="7" t="s">
-        <v>468</v>
-      </c>
-      <c r="E118" s="7" t="s">
-        <v>484</v>
-      </c>
-      <c r="F118" s="7" t="s">
-        <v>466</v>
-      </c>
-      <c r="G118" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="H118" s="7" t="s">
-        <v>471</v>
-      </c>
-      <c r="I118" s="7" t="s">
-        <v>472</v>
-      </c>
-      <c r="J118" s="7" t="s">
-        <v>485</v>
+        <v>475</v>
+      </c>
+      <c r="C118" t="s">
+        <v>476</v>
+      </c>
+      <c r="D118" t="s">
+        <v>461</v>
+      </c>
+      <c r="E118" t="s">
+        <v>477</v>
+      </c>
+      <c r="F118" t="s">
+        <v>459</v>
+      </c>
+      <c r="G118" t="s">
+        <v>303</v>
+      </c>
+      <c r="H118" t="s">
+        <v>464</v>
+      </c>
+      <c r="I118" t="s">
+        <v>465</v>
+      </c>
+      <c r="J118" t="s">
+        <v>478</v>
       </c>
     </row>
     <row r="119" spans="1:19">
       <c r="A119" s="5" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>486</v>
-      </c>
-      <c r="C119" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="D119" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="E119" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="F119" s="7" t="s">
-        <v>487</v>
-      </c>
-      <c r="G119" s="7" t="s">
-        <v>447</v>
-      </c>
-      <c r="H119" s="7" t="s">
-        <v>448</v>
-      </c>
-      <c r="I119" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="J119" s="7" t="s">
-        <v>488</v>
+        <v>479</v>
+      </c>
+      <c r="C119" t="s">
+        <v>203</v>
+      </c>
+      <c r="D119" t="s">
+        <v>204</v>
+      </c>
+      <c r="E119" t="s">
+        <v>278</v>
+      </c>
+      <c r="F119" t="s">
+        <v>480</v>
+      </c>
+      <c r="G119" t="s">
+        <v>440</v>
+      </c>
+      <c r="H119" t="s">
+        <v>441</v>
+      </c>
+      <c r="I119" t="s">
+        <v>181</v>
+      </c>
+      <c r="J119" t="s">
+        <v>481</v>
       </c>
     </row>
     <row r="120" spans="1:19">
       <c r="A120" s="5" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>489</v>
-      </c>
-      <c r="C120" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="D120" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="E120" s="7" t="s">
-        <v>447</v>
-      </c>
-      <c r="F120" s="7" t="s">
-        <v>448</v>
-      </c>
-      <c r="G120" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="H120" s="7" t="s">
-        <v>208</v>
+        <v>482</v>
+      </c>
+      <c r="C120" t="s">
+        <v>203</v>
+      </c>
+      <c r="D120" t="s">
+        <v>204</v>
+      </c>
+      <c r="E120" t="s">
+        <v>440</v>
+      </c>
+      <c r="F120" t="s">
+        <v>441</v>
+      </c>
+      <c r="G120" t="s">
+        <v>200</v>
+      </c>
+      <c r="H120" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="121" spans="1:19">
       <c r="A121" s="5" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>490</v>
-      </c>
-      <c r="C121" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="D121" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="E121" s="7" t="s">
-        <v>453</v>
-      </c>
-      <c r="F121" s="7" t="s">
-        <v>447</v>
-      </c>
-      <c r="G121" s="7" t="s">
-        <v>448</v>
-      </c>
-      <c r="H121" s="7" t="s">
-        <v>487</v>
-      </c>
-      <c r="I121" s="7" t="s">
-        <v>285</v>
+        <v>483</v>
+      </c>
+      <c r="C121" t="s">
+        <v>203</v>
+      </c>
+      <c r="D121" t="s">
+        <v>204</v>
+      </c>
+      <c r="E121" t="s">
+        <v>446</v>
+      </c>
+      <c r="F121" t="s">
+        <v>440</v>
+      </c>
+      <c r="G121" t="s">
+        <v>441</v>
+      </c>
+      <c r="H121" t="s">
+        <v>480</v>
+      </c>
+      <c r="I121" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="122" spans="1:19">
       <c r="A122" s="5" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>491</v>
-      </c>
-      <c r="C122" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="D122" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="E122" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="F122" s="7" t="s">
-        <v>471</v>
-      </c>
-      <c r="G122" s="7" t="s">
-        <v>472</v>
+        <v>484</v>
+      </c>
+      <c r="C122" t="s">
+        <v>172</v>
+      </c>
+      <c r="D122" t="s">
+        <v>173</v>
+      </c>
+      <c r="E122" t="s">
+        <v>174</v>
+      </c>
+      <c r="F122" t="s">
+        <v>464</v>
+      </c>
+      <c r="G122" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="123" spans="1:19">
       <c r="A123" s="5" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>492</v>
-      </c>
-      <c r="C123" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="D123" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="E123" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="F123" s="7" t="s">
-        <v>471</v>
-      </c>
-      <c r="G123" s="7" t="s">
-        <v>472</v>
+        <v>485</v>
+      </c>
+      <c r="C123" t="s">
+        <v>172</v>
+      </c>
+      <c r="D123" t="s">
+        <v>173</v>
+      </c>
+      <c r="E123" t="s">
+        <v>174</v>
+      </c>
+      <c r="F123" t="s">
+        <v>464</v>
+      </c>
+      <c r="G123" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="124" spans="1:19">
       <c r="A124" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="B124" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="B124" s="8" t="s">
+        <v>486</v>
+      </c>
+      <c r="C124" t="s">
+        <v>487</v>
+      </c>
+      <c r="D124" t="s">
+        <v>488</v>
+      </c>
+      <c r="E124" t="s">
+        <v>489</v>
+      </c>
+      <c r="F124" t="s">
+        <v>490</v>
+      </c>
+      <c r="G124" t="s">
+        <v>491</v>
+      </c>
+      <c r="H124" t="s">
+        <v>492</v>
+      </c>
+      <c r="I124" t="s">
         <v>493</v>
       </c>
-      <c r="C124" s="7" t="s">
+      <c r="J124" t="s">
         <v>494</v>
       </c>
-      <c r="D124" s="7" t="s">
+      <c r="K124" t="s">
         <v>495</v>
       </c>
-      <c r="E124" s="7" t="s">
-        <v>496</v>
-      </c>
-      <c r="F124" s="7" t="s">
-        <v>497</v>
-      </c>
-      <c r="G124" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="H124" s="7" t="s">
-        <v>499</v>
-      </c>
-      <c r="I124" s="7" t="s">
-        <v>500</v>
-      </c>
-      <c r="J124" s="7" t="s">
-        <v>501</v>
-      </c>
-      <c r="K124" s="7" t="s">
-        <v>502</v>
-      </c>
-      <c r="L124" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="M124" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="N124" s="7" t="s">
-        <v>212</v>
+      <c r="L124" t="s">
+        <v>203</v>
+      </c>
+      <c r="M124" t="s">
+        <v>204</v>
+      </c>
+      <c r="N124" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="125" spans="1:19">
       <c r="A125" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="B125" s="9" t="s">
-        <v>503</v>
-      </c>
-      <c r="C125" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="B125" s="8" t="s">
+        <v>496</v>
+      </c>
+      <c r="C125" t="s">
+        <v>487</v>
+      </c>
+      <c r="D125" t="s">
+        <v>488</v>
+      </c>
+      <c r="E125" t="s">
+        <v>489</v>
+      </c>
+      <c r="F125" t="s">
+        <v>490</v>
+      </c>
+      <c r="G125" t="s">
+        <v>491</v>
+      </c>
+      <c r="H125" t="s">
+        <v>492</v>
+      </c>
+      <c r="I125" t="s">
+        <v>493</v>
+      </c>
+      <c r="J125" t="s">
         <v>494</v>
       </c>
-      <c r="D125" s="7" t="s">
+      <c r="K125" t="s">
         <v>495</v>
       </c>
-      <c r="E125" s="7" t="s">
-        <v>496</v>
-      </c>
-      <c r="F125" s="7" t="s">
+      <c r="L125" t="s">
         <v>497</v>
       </c>
-      <c r="G125" s="7" t="s">
+      <c r="M125" t="s">
         <v>498</v>
       </c>
-      <c r="H125" s="7" t="s">
+      <c r="N125" t="s">
         <v>499</v>
       </c>
-      <c r="I125" s="7" t="s">
+      <c r="O125" t="s">
         <v>500</v>
-      </c>
-      <c r="J125" s="7" t="s">
-        <v>501</v>
-      </c>
-      <c r="K125" s="7" t="s">
-        <v>502</v>
-      </c>
-      <c r="L125" s="7" t="s">
-        <v>504</v>
-      </c>
-      <c r="M125" s="7" t="s">
-        <v>505</v>
-      </c>
-      <c r="N125" s="7" t="s">
-        <v>506</v>
-      </c>
-      <c r="O125" s="7" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="126" spans="1:19">
       <c r="A126" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="B126" s="9" t="s">
-        <v>508</v>
-      </c>
-      <c r="C126" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="B126" s="8" t="s">
+        <v>501</v>
+      </c>
+      <c r="C126" t="s">
+        <v>487</v>
+      </c>
+      <c r="D126" t="s">
+        <v>488</v>
+      </c>
+      <c r="E126" t="s">
+        <v>489</v>
+      </c>
+      <c r="F126" t="s">
+        <v>490</v>
+      </c>
+      <c r="G126" t="s">
+        <v>491</v>
+      </c>
+      <c r="H126" t="s">
+        <v>492</v>
+      </c>
+      <c r="I126" t="s">
+        <v>493</v>
+      </c>
+      <c r="J126" t="s">
         <v>494</v>
       </c>
-      <c r="D126" s="7" t="s">
+      <c r="K126" t="s">
         <v>495</v>
       </c>
-      <c r="E126" s="7" t="s">
-        <v>496</v>
-      </c>
-      <c r="F126" s="7" t="s">
+      <c r="L126" t="s">
         <v>497</v>
       </c>
-      <c r="G126" s="7" t="s">
+      <c r="M126" t="s">
         <v>498</v>
       </c>
-      <c r="H126" s="7" t="s">
+      <c r="N126" t="s">
         <v>499</v>
-      </c>
-      <c r="I126" s="7" t="s">
-        <v>500</v>
-      </c>
-      <c r="J126" s="7" t="s">
-        <v>501</v>
-      </c>
-      <c r="K126" s="7" t="s">
-        <v>502</v>
-      </c>
-      <c r="L126" s="7" t="s">
-        <v>504</v>
-      </c>
-      <c r="M126" s="7" t="s">
-        <v>505</v>
-      </c>
-      <c r="N126" s="7" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="127" spans="1:19">
       <c r="A127" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="B127" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B127" s="8" t="s">
+        <v>502</v>
+      </c>
+      <c r="C127" t="s">
+        <v>487</v>
+      </c>
+      <c r="D127" t="s">
+        <v>488</v>
+      </c>
+      <c r="E127" t="s">
+        <v>489</v>
+      </c>
+      <c r="F127" t="s">
+        <v>490</v>
+      </c>
+      <c r="G127" t="s">
+        <v>491</v>
+      </c>
+      <c r="H127" t="s">
+        <v>492</v>
+      </c>
+      <c r="I127" t="s">
+        <v>493</v>
+      </c>
+      <c r="J127" t="s">
+        <v>494</v>
+      </c>
+      <c r="K127" t="s">
+        <v>495</v>
+      </c>
+      <c r="L127" t="s">
+        <v>503</v>
+      </c>
+      <c r="M127" t="s">
+        <v>504</v>
+      </c>
+      <c r="N127" t="s">
+        <v>505</v>
+      </c>
+      <c r="O127" t="s">
+        <v>506</v>
+      </c>
+      <c r="P127" t="s">
+        <v>507</v>
+      </c>
+      <c r="Q127" t="s">
+        <v>508</v>
+      </c>
+      <c r="R127" t="s">
         <v>509</v>
       </c>
-      <c r="C127" s="7" t="s">
-        <v>494</v>
-      </c>
-      <c r="D127" s="7" t="s">
-        <v>495</v>
-      </c>
-      <c r="E127" s="7" t="s">
-        <v>496</v>
-      </c>
-      <c r="F127" s="7" t="s">
-        <v>497</v>
-      </c>
-      <c r="G127" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="H127" s="7" t="s">
-        <v>499</v>
-      </c>
-      <c r="I127" s="7" t="s">
-        <v>500</v>
-      </c>
-      <c r="J127" s="7" t="s">
-        <v>501</v>
-      </c>
-      <c r="K127" s="7" t="s">
-        <v>502</v>
-      </c>
-      <c r="L127" s="7" t="s">
+      <c r="S127" t="s">
         <v>510</v>
-      </c>
-      <c r="M127" s="7" t="s">
-        <v>511</v>
-      </c>
-      <c r="N127" s="7" t="s">
-        <v>512</v>
-      </c>
-      <c r="O127" s="7" t="s">
-        <v>513</v>
-      </c>
-      <c r="P127" s="7" t="s">
-        <v>514</v>
-      </c>
-      <c r="Q127" s="7" t="s">
-        <v>515</v>
-      </c>
-      <c r="R127" s="7" t="s">
-        <v>516</v>
-      </c>
-      <c r="S127" s="7" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="128" spans="1:19">
       <c r="A128" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="B128" s="9" t="s">
-        <v>518</v>
-      </c>
-      <c r="C128" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="B128" s="8" t="s">
+        <v>511</v>
+      </c>
+      <c r="C128" t="s">
+        <v>487</v>
+      </c>
+      <c r="D128" t="s">
+        <v>488</v>
+      </c>
+      <c r="E128" t="s">
+        <v>489</v>
+      </c>
+      <c r="F128" t="s">
+        <v>490</v>
+      </c>
+      <c r="G128" t="s">
+        <v>491</v>
+      </c>
+      <c r="H128" t="s">
+        <v>492</v>
+      </c>
+      <c r="I128" t="s">
+        <v>512</v>
+      </c>
+      <c r="J128" t="s">
+        <v>513</v>
+      </c>
+      <c r="K128" t="s">
+        <v>493</v>
+      </c>
+      <c r="L128" t="s">
         <v>494</v>
       </c>
-      <c r="D128" s="7" t="s">
+      <c r="M128" t="s">
         <v>495</v>
       </c>
-      <c r="E128" s="7" t="s">
-        <v>496</v>
-      </c>
-      <c r="F128" s="7" t="s">
-        <v>497</v>
-      </c>
-      <c r="G128" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="H128" s="7" t="s">
-        <v>499</v>
-      </c>
-      <c r="I128" s="7" t="s">
-        <v>519</v>
-      </c>
-      <c r="J128" s="7" t="s">
-        <v>520</v>
-      </c>
-      <c r="K128" s="7" t="s">
-        <v>500</v>
-      </c>
-      <c r="L128" s="7" t="s">
-        <v>501</v>
-      </c>
-      <c r="M128" s="7" t="s">
-        <v>502</v>
-      </c>
-      <c r="N128" s="7" t="s">
-        <v>521</v>
-      </c>
-      <c r="O128" s="7" t="s">
-        <v>522</v>
+      <c r="N128" t="s">
+        <v>514</v>
+      </c>
+      <c r="O128" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="129" spans="1:20">
       <c r="A129" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="B129" s="9" t="s">
-        <v>523</v>
-      </c>
-      <c r="C129" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="B129" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="C129" t="s">
+        <v>487</v>
+      </c>
+      <c r="D129" t="s">
+        <v>488</v>
+      </c>
+      <c r="E129" t="s">
+        <v>489</v>
+      </c>
+      <c r="F129" t="s">
+        <v>490</v>
+      </c>
+      <c r="G129" t="s">
+        <v>491</v>
+      </c>
+      <c r="H129" t="s">
+        <v>492</v>
+      </c>
+      <c r="I129" t="s">
+        <v>493</v>
+      </c>
+      <c r="J129" t="s">
         <v>494</v>
       </c>
-      <c r="D129" s="7" t="s">
+      <c r="K129" t="s">
         <v>495</v>
       </c>
-      <c r="E129" s="7" t="s">
-        <v>496</v>
-      </c>
-      <c r="F129" s="7" t="s">
+      <c r="L129" t="s">
         <v>497</v>
       </c>
-      <c r="G129" s="7" t="s">
+      <c r="M129" t="s">
         <v>498</v>
-      </c>
-      <c r="H129" s="7" t="s">
-        <v>499</v>
-      </c>
-      <c r="I129" s="7" t="s">
-        <v>500</v>
-      </c>
-      <c r="J129" s="7" t="s">
-        <v>501</v>
-      </c>
-      <c r="K129" s="7" t="s">
-        <v>502</v>
-      </c>
-      <c r="L129" s="7" t="s">
-        <v>504</v>
-      </c>
-      <c r="M129" s="7" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="130" spans="1:20">
       <c r="A130" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="B130" s="9" t="s">
-        <v>524</v>
-      </c>
-      <c r="C130" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="B130" s="8" t="s">
+        <v>517</v>
+      </c>
+      <c r="C130" t="s">
+        <v>487</v>
+      </c>
+      <c r="D130" t="s">
+        <v>488</v>
+      </c>
+      <c r="E130" t="s">
+        <v>489</v>
+      </c>
+      <c r="F130" t="s">
+        <v>490</v>
+      </c>
+      <c r="G130" t="s">
+        <v>491</v>
+      </c>
+      <c r="H130" t="s">
+        <v>492</v>
+      </c>
+      <c r="I130" t="s">
+        <v>493</v>
+      </c>
+      <c r="J130" t="s">
         <v>494</v>
       </c>
-      <c r="D130" s="7" t="s">
+      <c r="K130" t="s">
         <v>495</v>
       </c>
-      <c r="E130" s="7" t="s">
-        <v>496</v>
-      </c>
-      <c r="F130" s="7" t="s">
+      <c r="L130" t="s">
         <v>497</v>
       </c>
-      <c r="G130" s="7" t="s">
+      <c r="M130" t="s">
         <v>498</v>
       </c>
-      <c r="H130" s="7" t="s">
-        <v>499</v>
-      </c>
-      <c r="I130" s="7" t="s">
-        <v>500</v>
-      </c>
-      <c r="J130" s="7" t="s">
-        <v>501</v>
-      </c>
-      <c r="K130" s="7" t="s">
-        <v>502</v>
-      </c>
-      <c r="L130" s="7" t="s">
-        <v>504</v>
-      </c>
-      <c r="M130" s="7" t="s">
-        <v>505</v>
-      </c>
-      <c r="N130" s="7" t="s">
-        <v>525</v>
-      </c>
-      <c r="O130" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="P130" s="7" t="s">
-        <v>526</v>
+      <c r="N130" t="s">
+        <v>518</v>
+      </c>
+      <c r="O130" t="s">
+        <v>173</v>
+      </c>
+      <c r="P130" t="s">
+        <v>519</v>
       </c>
     </row>
     <row r="131" spans="1:20">
       <c r="A131" s="5" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="B131" s="6" t="s">
+        <v>520</v>
+      </c>
+      <c r="C131" t="s">
+        <v>521</v>
+      </c>
+      <c r="D131" t="s">
+        <v>522</v>
+      </c>
+      <c r="E131" t="s">
+        <v>523</v>
+      </c>
+      <c r="F131" t="s">
+        <v>524</v>
+      </c>
+      <c r="G131" t="s">
+        <v>525</v>
+      </c>
+      <c r="H131" t="s">
+        <v>526</v>
+      </c>
+      <c r="I131" t="s">
         <v>527</v>
       </c>
-      <c r="C131" s="7" t="s">
+      <c r="J131" t="s">
         <v>528</v>
       </c>
-      <c r="D131" s="7" t="s">
+      <c r="K131" t="s">
         <v>529</v>
       </c>
-      <c r="E131" s="7" t="s">
+      <c r="L131" t="s">
         <v>530</v>
       </c>
-      <c r="F131" s="7" t="s">
+      <c r="M131" t="s">
         <v>531</v>
       </c>
-      <c r="G131" s="7" t="s">
+      <c r="N131" t="s">
         <v>532</v>
-      </c>
-      <c r="H131" s="7" t="s">
-        <v>533</v>
-      </c>
-      <c r="I131" s="7" t="s">
-        <v>534</v>
-      </c>
-      <c r="J131" s="7" t="s">
-        <v>535</v>
-      </c>
-      <c r="K131" s="7" t="s">
-        <v>536</v>
-      </c>
-      <c r="L131" s="7" t="s">
-        <v>537</v>
-      </c>
-      <c r="M131" s="7" t="s">
-        <v>538</v>
-      </c>
-      <c r="N131" s="7" t="s">
-        <v>539</v>
       </c>
     </row>
     <row r="132" spans="1:20">
       <c r="A132" s="5" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="B132" s="6" t="s">
+        <v>533</v>
+      </c>
+      <c r="C132" t="s">
+        <v>534</v>
+      </c>
+      <c r="D132" t="s">
+        <v>535</v>
+      </c>
+      <c r="E132" t="s">
+        <v>536</v>
+      </c>
+      <c r="F132" t="s">
+        <v>537</v>
+      </c>
+      <c r="G132" t="s">
+        <v>538</v>
+      </c>
+      <c r="H132" t="s">
+        <v>539</v>
+      </c>
+      <c r="I132" t="s">
         <v>540</v>
       </c>
-      <c r="C132" s="7" t="s">
+      <c r="J132" t="s">
         <v>541</v>
       </c>
-      <c r="D132" s="7" t="s">
+      <c r="K132" t="s">
         <v>542</v>
       </c>
-      <c r="E132" s="7" t="s">
+      <c r="L132" t="s">
         <v>543</v>
       </c>
-      <c r="F132" s="7" t="s">
+      <c r="M132" t="s">
         <v>544</v>
       </c>
-      <c r="G132" s="7" t="s">
+      <c r="N132" t="s">
         <v>545</v>
       </c>
-      <c r="H132" s="7" t="s">
+      <c r="O132" t="s">
         <v>546</v>
       </c>
-      <c r="I132" s="7" t="s">
+      <c r="P132" t="s">
         <v>547</v>
       </c>
-      <c r="J132" s="7" t="s">
+      <c r="Q132" t="s">
         <v>548</v>
       </c>
-      <c r="K132" s="7" t="s">
+      <c r="R132" t="s">
         <v>549</v>
-      </c>
-      <c r="L132" s="7" t="s">
-        <v>550</v>
-      </c>
-      <c r="M132" s="7" t="s">
-        <v>551</v>
-      </c>
-      <c r="N132" s="7" t="s">
-        <v>552</v>
-      </c>
-      <c r="O132" s="7" t="s">
-        <v>553</v>
-      </c>
-      <c r="P132" s="7" t="s">
-        <v>554</v>
-      </c>
-      <c r="Q132" s="7" t="s">
-        <v>555</v>
-      </c>
-      <c r="R132" s="7" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="133" spans="1:20">
       <c r="A133" s="5" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="B133" s="6" t="s">
+        <v>550</v>
+      </c>
+      <c r="C133" t="s">
+        <v>534</v>
+      </c>
+      <c r="D133" t="s">
+        <v>535</v>
+      </c>
+      <c r="E133" t="s">
+        <v>536</v>
+      </c>
+      <c r="F133" t="s">
+        <v>537</v>
+      </c>
+      <c r="G133" t="s">
+        <v>538</v>
+      </c>
+      <c r="H133" t="s">
+        <v>539</v>
+      </c>
+      <c r="I133" t="s">
+        <v>540</v>
+      </c>
+      <c r="J133" t="s">
+        <v>541</v>
+      </c>
+      <c r="K133" t="s">
+        <v>542</v>
+      </c>
+      <c r="L133" t="s">
+        <v>543</v>
+      </c>
+      <c r="M133" t="s">
+        <v>544</v>
+      </c>
+      <c r="N133" t="s">
+        <v>545</v>
+      </c>
+      <c r="O133" t="s">
+        <v>546</v>
+      </c>
+      <c r="P133" t="s">
+        <v>547</v>
+      </c>
+      <c r="Q133" t="s">
+        <v>548</v>
+      </c>
+      <c r="R133" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="134" spans="1:20">
+      <c r="A134" s="7" t="s">
+        <v>551</v>
+      </c>
+      <c r="B134" s="7" t="s">
+        <v>551</v>
+      </c>
+      <c r="C134" s="7" t="s">
+        <v>552</v>
+      </c>
+      <c r="D134" s="7" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="135" spans="1:20">
+      <c r="A135" s="7" t="s">
+        <v>554</v>
+      </c>
+      <c r="B135" s="7" t="s">
+        <v>554</v>
+      </c>
+      <c r="C135" s="7" t="s">
+        <v>555</v>
+      </c>
+      <c r="D135" s="7" t="s">
+        <v>556</v>
+      </c>
+      <c r="E135" s="7" t="s">
         <v>557</v>
       </c>
-      <c r="C133" s="7" t="s">
-        <v>541</v>
-      </c>
-      <c r="D133" s="7" t="s">
-        <v>542</v>
-      </c>
-      <c r="E133" s="7" t="s">
-        <v>543</v>
-      </c>
-      <c r="F133" s="7" t="s">
-        <v>544</v>
-      </c>
-      <c r="G133" s="7" t="s">
-        <v>545</v>
-      </c>
-      <c r="H133" s="7" t="s">
-        <v>546</v>
-      </c>
-      <c r="I133" s="7" t="s">
-        <v>547</v>
-      </c>
-      <c r="J133" s="7" t="s">
-        <v>548</v>
-      </c>
-      <c r="K133" s="7" t="s">
-        <v>549</v>
-      </c>
-      <c r="L133" s="7" t="s">
-        <v>550</v>
-      </c>
-      <c r="M133" s="7" t="s">
-        <v>551</v>
-      </c>
-      <c r="N133" s="7" t="s">
-        <v>552</v>
-      </c>
-      <c r="O133" s="7" t="s">
-        <v>553</v>
-      </c>
-      <c r="P133" s="7" t="s">
-        <v>554</v>
-      </c>
-      <c r="Q133" s="7" t="s">
+      <c r="F135" s="7" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="136" spans="1:20">
+      <c r="A136" s="7" t="s">
+        <v>559</v>
+      </c>
+      <c r="B136" s="7" t="s">
+        <v>559</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F136" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G136" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H136" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I136" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J136" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="K136" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="L136" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="M136" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="N136" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="O136" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="P136" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="Q136" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="R136" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="S136" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="T136" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="137" spans="1:20">
+      <c r="A137" s="7" t="s">
+        <v>560</v>
+      </c>
+      <c r="B137" s="7" t="s">
+        <v>560</v>
+      </c>
+      <c r="C137" s="7" t="s">
         <v>555</v>
       </c>
-      <c r="R133" s="7" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="134" spans="1:20">
-      <c r="A134" s="8" t="s">
-        <v>558</v>
-      </c>
-      <c r="B134" s="8" t="s">
-        <v>558</v>
-      </c>
-      <c r="C134" s="8" t="s">
-        <v>559</v>
-      </c>
-      <c r="D134" s="8" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="135" spans="1:20">
-      <c r="A135" s="8" t="s">
+    </row>
+    <row r="138" spans="1:20">
+      <c r="A138" s="7" t="s">
         <v>561</v>
       </c>
-      <c r="B135" s="8" t="s">
+      <c r="B138" s="7" t="s">
         <v>561</v>
       </c>
-      <c r="C135" s="8" t="s">
+      <c r="C138" s="7" t="s">
         <v>562</v>
       </c>
-      <c r="D135" s="8" t="s">
+      <c r="D138" s="7" t="s">
         <v>563</v>
       </c>
-      <c r="E135" s="8" t="s">
+      <c r="E138" s="7" t="s">
         <v>564</v>
       </c>
-      <c r="F135" s="8" t="s">
+      <c r="F138" s="7" t="s">
         <v>565</v>
-      </c>
-    </row>
-    <row r="136" spans="1:20">
-      <c r="A136" s="8" t="s">
-        <v>566</v>
-      </c>
-      <c r="B136" s="8" t="s">
-        <v>566</v>
-      </c>
-      <c r="C136" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E136" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F136" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G136" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="H136" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="I136" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="J136" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="K136" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="L136" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="M136" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="N136" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="O136" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="P136" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="Q136" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="R136" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="S136" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="T136" s="1" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="137" spans="1:20">
-      <c r="A137" s="8" t="s">
-        <v>567</v>
-      </c>
-      <c r="B137" s="8" t="s">
-        <v>567</v>
-      </c>
-      <c r="C137" s="8" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="138" spans="1:20">
-      <c r="A138" s="8" t="s">
-        <v>568</v>
-      </c>
-      <c r="B138" s="8" t="s">
-        <v>568</v>
-      </c>
-      <c r="C138" s="8" t="s">
-        <v>569</v>
-      </c>
-      <c r="D138" s="8" t="s">
-        <v>570</v>
-      </c>
-      <c r="E138" s="8" t="s">
-        <v>571</v>
-      </c>
-      <c r="F138" s="8" t="s">
-        <v>572</v>
       </c>
     </row>
   </sheetData>
